--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F950"/>
+  <dimension ref="A1:F961"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -18181,10 +18181,10 @@
         <v>ניהול מפות - ביצירת/עריכת אזור: הצגה ועדכון של רשימת נקודות הציון של האזור בפורמט NXXXX.XXX EYYYYY.YYY</v>
       </c>
       <c r="E889" t="str">
-        <v/>
+        <v>כן</v>
       </c>
       <c r="F889" t="str">
-        <v/>
+        <v>20af89f · v1.0.134</v>
       </c>
     </row>
     <row r="890">
@@ -19407,9 +19407,229 @@
         <v>commit a03c8b0 · v1.0.160 · נדחף ל-main</v>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" t="str">
+        <v/>
+      </c>
+      <c r="B951" t="str">
+        <v>2026-09-01 10:20</v>
+      </c>
+      <c r="C951" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D951" t="str">
+        <v>תלת מימד: סרגל הגובה לא יושב על המישור ולא תואם לגובה של נקודות הגישה</v>
+      </c>
+      <c r="E951" t="str">
+        <v/>
+      </c>
+      <c r="F951" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="str">
+        <v/>
+      </c>
+      <c r="B952" t="str">
+        <v>2026-09-01 10:20</v>
+      </c>
+      <c r="C952" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D952" t="str">
+        <v>תלת מימד: רכיבים אוויריים לא מוצגים בגובה נכון יחסית לנקודות הגישה וההקפה</v>
+      </c>
+      <c r="E952" t="str">
+        <v/>
+      </c>
+      <c r="F952" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="str">
+        <v/>
+      </c>
+      <c r="B953" t="str">
+        <v>2026-09-01 10:20</v>
+      </c>
+      <c r="C953" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D953" t="str">
+        <v>רכיב אווירי בטיפוס/נמיכה: חץ לבן למעלה/למטה ליד האייקון</v>
+      </c>
+      <c r="E953" t="str">
+        <v/>
+      </c>
+      <c r="F953" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="str">
+        <v/>
+      </c>
+      <c r="B954" t="str">
+        <v>2026-09-01 10:20</v>
+      </c>
+      <c r="C954" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D954" t="str">
+        <v>פילטר תמונ"א: בחירת נתונים להצגה ליד האייקון (או"ק / גובה / מהירות)</v>
+      </c>
+      <c r="E954" t="str">
+        <v/>
+      </c>
+      <c r="F954" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="str">
+        <v/>
+      </c>
+      <c r="B955" t="str">
+        <v>2026-09-01 10:38</v>
+      </c>
+      <c r="C955" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D955" t="str">
+        <v>הגנ"ש: סולם איכות עמידה במשימה באחוזים 0-100 (במקום סולם 0-3)</v>
+      </c>
+      <c r="E955" t="str">
+        <v/>
+      </c>
+      <c r="F955" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="str">
+        <v/>
+      </c>
+      <c r="B956" t="str">
+        <v>2026-09-01 10:38</v>
+      </c>
+      <c r="C956" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D956" t="str">
+        <v>הגנ"ש: הוספת טווח גובה לאמצעי גילוי ואש (קטלוג + דריסה בפריסה)</v>
+      </c>
+      <c r="E956" t="str">
+        <v/>
+      </c>
+      <c r="F956" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="str">
+        <v/>
+      </c>
+      <c r="B957" t="str">
+        <v>2026-09-01 10:38</v>
+      </c>
+      <c r="C957" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D957" t="str">
+        <v>הגנ"ש: זמן זמינות פ"מ משלושה מקורות - תמונ"א, חישוב מבסיס ב-450 קשר, וידני שדורס את הכל</v>
+      </c>
+      <c r="E957" t="str">
+        <v/>
+      </c>
+      <c r="F957" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="str">
+        <v/>
+      </c>
+      <c r="B958" t="str">
+        <v>2026-09-09 08:24</v>
+      </c>
+      <c r="C958" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D958" t="str">
+        <v>תלת מימד: מסלול סגור יוצג באדום</v>
+      </c>
+      <c r="E958" t="str">
+        <v/>
+      </c>
+      <c r="F958" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="str">
+        <v/>
+      </c>
+      <c r="B959" t="str">
+        <v>2026-09-09 08:24</v>
+      </c>
+      <c r="C959" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D959" t="str">
+        <v>תלת מימד: הנמכה רציפה/לינארית בהקפה במקום ירידה פתאומית</v>
+      </c>
+      <c r="E959" t="str">
+        <v/>
+      </c>
+      <c r="F959" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="str">
+        <v/>
+      </c>
+      <c r="B960" t="str">
+        <v>2026-09-09 08:24</v>
+      </c>
+      <c r="C960" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D960" t="str">
+        <v>תלת מימד: סרגל הגבהים לא יושב על משטח הדאטום ולא תואם לגובה נקודות המעבר (שמשון, הקפת תל נוף)</v>
+      </c>
+      <c r="E960" t="str">
+        <v/>
+      </c>
+      <c r="F960" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="str">
+        <v/>
+      </c>
+      <c r="B961" t="str">
+        <v>2026-09-09 17:52</v>
+      </c>
+      <c r="C961" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D961" t="str">
+        <v>קימוט, דחיפה לגיט ופריסה ל-Railway של תיקוני התלת מימד והתמונ"א</v>
+      </c>
+      <c r="E961" t="str">
+        <v/>
+      </c>
+      <c r="F961" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F950"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F961"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F961"/>
+  <dimension ref="A1:F967"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -19552,13 +19552,13 @@
         <v/>
       </c>
       <c r="B958" t="str">
-        <v>2026-09-09 08:24</v>
+        <v>2026-09-09 01:06</v>
       </c>
       <c r="C958" t="str">
         <v>תכולה חדשה</v>
       </c>
       <c r="D958" t="str">
-        <v>תלת מימד: מסלול סגור יוצג באדום</v>
+        <v>ניהול רכבים ואישורי כניסה - חלון ניהול נהגים/רכבים בעמדת ניהול שדה תעופה (שם, ת.ז., אישור לאזורים, סוג רכב, רישוי, תפקיד הסעה, תוקף, סטטוס, מאשר)</v>
       </c>
       <c r="E958" t="str">
         <v/>
@@ -19572,13 +19572,13 @@
         <v/>
       </c>
       <c r="B959" t="str">
-        <v>2026-09-09 08:24</v>
+        <v>2026-09-09 01:06</v>
       </c>
       <c r="C959" t="str">
-        <v>שיפור לתכולה קיימת</v>
+        <v>תכולה חדשה</v>
       </c>
       <c r="D959" t="str">
-        <v>תלת מימד: הנמכה רציפה/לינארית בהקפה במקום ירידה פתאומית</v>
+        <v>תת תפריט "ניהול רכבים" בתפריט תצוגה ליד "הצגת רכבים" - פותח את חלון ניהול הרכבים</v>
       </c>
       <c r="E959" t="str">
         <v/>
@@ -19592,13 +19592,13 @@
         <v/>
       </c>
       <c r="B960" t="str">
-        <v>2026-09-09 08:24</v>
+        <v>2026-09-09 01:06</v>
       </c>
       <c r="C960" t="str">
-        <v>תקלה</v>
+        <v>תכולה חדשה</v>
       </c>
       <c r="D960" t="str">
-        <v>תלת מימד: סרגל הגבהים לא יושב על משטח הדאטום ולא תואם לגובה נקודות המעבר (שמשון, הקפת תל נוף)</v>
+        <v>סטטוס אישור כניסה אוטומטי לפי תאריכי אישור/פקיעה עם אפשרות דריסה ידנית (מאושר/לא מאושר/בבדיקה/נפסל)</v>
       </c>
       <c r="E960" t="str">
         <v/>
@@ -19612,24 +19612,144 @@
         <v/>
       </c>
       <c r="B961" t="str">
+        <v>2026-09-09 01:06</v>
+      </c>
+      <c r="C961" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D961" t="str">
+        <v>טבלת נסיעות לרכב (מאיפה/לאן) עם היסטוריה ונסיעות עתידיות + פרמטרים בניהול שדה (אזורים, תפקידי הסעה, סוגי רכב)</v>
+      </c>
+      <c r="E961" t="str">
+        <v/>
+      </c>
+      <c r="F961" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="str">
+        <v/>
+      </c>
+      <c r="B962" t="str">
+        <v>2026-09-09 01:21</v>
+      </c>
+      <c r="C962" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D962" t="str">
+        <v>סנכרון תיעוד אחרי v1.0.163 - משטחי גובה, הנמכה רציפה, מסלול סגור ומגמת תמונ"א</v>
+      </c>
+      <c r="E962" t="str">
+        <v/>
+      </c>
+      <c r="F962" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="str">
+        <v/>
+      </c>
+      <c r="B963" t="str">
+        <v>2026-09-09 08:24</v>
+      </c>
+      <c r="C963" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D963" t="str">
+        <v>תלת מימד: מסלול סגור יוצג באדום</v>
+      </c>
+      <c r="E963" t="str">
+        <v/>
+      </c>
+      <c r="F963" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="str">
+        <v/>
+      </c>
+      <c r="B964" t="str">
+        <v>2026-09-09 08:24</v>
+      </c>
+      <c r="C964" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D964" t="str">
+        <v>תלת מימד: הנמכה רציפה/לינארית בהקפה במקום ירידה פתאומית</v>
+      </c>
+      <c r="E964" t="str">
+        <v/>
+      </c>
+      <c r="F964" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="str">
+        <v/>
+      </c>
+      <c r="B965" t="str">
+        <v>2026-09-09 08:24</v>
+      </c>
+      <c r="C965" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D965" t="str">
+        <v>תלת מימד: סרגל הגבהים לא יושב על משטח הדאטום ולא תואם לגובה נקודות המעבר (שמשון, הקפת תל נוף)</v>
+      </c>
+      <c r="E965" t="str">
+        <v/>
+      </c>
+      <c r="F965" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="str">
+        <v/>
+      </c>
+      <c r="B966" t="str">
         <v>2026-09-09 17:52</v>
       </c>
-      <c r="C961" t="str">
-        <v>שיפור לתכולה קיימת</v>
-      </c>
-      <c r="D961" t="str">
+      <c r="C966" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D966" t="str">
         <v>קימוט, דחיפה לגיט ופריסה ל-Railway של תיקוני התלת מימד והתמונ"א</v>
       </c>
-      <c r="E961" t="str">
-        <v/>
-      </c>
-      <c r="F961" t="str">
+      <c r="E966" t="str">
+        <v/>
+      </c>
+      <c r="F966" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="str">
+        <v/>
+      </c>
+      <c r="B967" t="str">
+        <v>2026-09-09 17:53</v>
+      </c>
+      <c r="C967" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D967" t="str">
+        <v>בעמדת ניהול שדה תעופה באנרי ההתראות עולים אחד על השני (חפיפה) - צריך לסדר אותם בלי לכסות זה את זה</v>
+      </c>
+      <c r="E967" t="str">
+        <v/>
+      </c>
+      <c r="F967" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F961"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F967"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F967"/>
+  <dimension ref="A1:F970"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -19652,13 +19652,13 @@
         <v/>
       </c>
       <c r="B963" t="str">
-        <v>2026-09-09 08:24</v>
+        <v>2026-09-09 01:34</v>
       </c>
       <c r="C963" t="str">
-        <v>תכולה חדשה</v>
+        <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D963" t="str">
-        <v>תלת מימד: מסלול סגור יוצג באדום</v>
+        <v>פריסת v1.0.164 ל-Railway ליישור מספר הגרסה במסך הכניסה</v>
       </c>
       <c r="E963" t="str">
         <v/>
@@ -19672,13 +19672,13 @@
         <v/>
       </c>
       <c r="B964" t="str">
-        <v>2026-09-09 08:24</v>
+        <v>2026-09-09 01:34</v>
       </c>
       <c r="C964" t="str">
         <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D964" t="str">
-        <v>תלת מימד: הנמכה רציפה/לינארית בהקפה במקום ירידה פתאומית</v>
+        <v>הפצה לנמענים: חלוקת רשימת העמדות לקטגוריות לפי בסיס אב; ב"מ הכל מכווץ חוץ מהבסיס שלי</v>
       </c>
       <c r="E964" t="str">
         <v/>
@@ -19692,13 +19692,13 @@
         <v/>
       </c>
       <c r="B965" t="str">
-        <v>2026-09-09 08:24</v>
+        <v>2026-09-09 01:34</v>
       </c>
       <c r="C965" t="str">
-        <v>תקלה</v>
+        <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D965" t="str">
-        <v>תלת מימד: סרגל הגבהים לא יושב על משטח הדאטום ולא תואם לגובה נקודות המעבר (שמשון, הקפת תל נוף)</v>
+        <v>הפצה לנמענים: סימון בסיס אב מסמן את כל העמדות שתחתיו</v>
       </c>
       <c r="E965" t="str">
         <v/>
@@ -19712,13 +19712,13 @@
         <v/>
       </c>
       <c r="B966" t="str">
-        <v>2026-09-09 17:52</v>
+        <v>2026-09-09 08:24</v>
       </c>
       <c r="C966" t="str">
-        <v>שיפור לתכולה קיימת</v>
+        <v>תכולה חדשה</v>
       </c>
       <c r="D966" t="str">
-        <v>קימוט, דחיפה לגיט ופריסה ל-Railway של תיקוני התלת מימד והתמונ"א</v>
+        <v>תלת מימד: מסלול סגור יוצג באדום</v>
       </c>
       <c r="E966" t="str">
         <v/>
@@ -19732,24 +19732,84 @@
         <v/>
       </c>
       <c r="B967" t="str">
+        <v>2026-09-09 08:24</v>
+      </c>
+      <c r="C967" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D967" t="str">
+        <v>תלת מימד: הנמכה רציפה/לינארית בהקפה במקום ירידה פתאומית</v>
+      </c>
+      <c r="E967" t="str">
+        <v/>
+      </c>
+      <c r="F967" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="str">
+        <v/>
+      </c>
+      <c r="B968" t="str">
+        <v>2026-09-09 08:24</v>
+      </c>
+      <c r="C968" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D968" t="str">
+        <v>תלת מימד: סרגל הגבהים לא יושב על משטח הדאטום ולא תואם לגובה נקודות המעבר (שמשון, הקפת תל נוף)</v>
+      </c>
+      <c r="E968" t="str">
+        <v/>
+      </c>
+      <c r="F968" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="str">
+        <v/>
+      </c>
+      <c r="B969" t="str">
+        <v>2026-09-09 17:52</v>
+      </c>
+      <c r="C969" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D969" t="str">
+        <v>קימוט, דחיפה לגיט ופריסה ל-Railway של תיקוני התלת מימד והתמונ"א</v>
+      </c>
+      <c r="E969" t="str">
+        <v/>
+      </c>
+      <c r="F969" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="str">
+        <v/>
+      </c>
+      <c r="B970" t="str">
         <v>2026-09-09 17:53</v>
       </c>
-      <c r="C967" t="str">
-        <v>תקלה</v>
-      </c>
-      <c r="D967" t="str">
+      <c r="C970" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D970" t="str">
         <v>בעמדת ניהול שדה תעופה באנרי ההתראות עולים אחד על השני (חפיפה) - צריך לסדר אותם בלי לכסות זה את זה</v>
       </c>
-      <c r="E967" t="str">
-        <v/>
-      </c>
-      <c r="F967" t="str">
+      <c r="E970" t="str">
+        <v/>
+      </c>
+      <c r="F970" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F967"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F970"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F970"/>
+  <dimension ref="A1:F971"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -19807,9 +19807,29 @@
         <v/>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" t="str">
+        <v/>
+      </c>
+      <c r="B971" t="str">
+        <v>2026-09-10 13:37</v>
+      </c>
+      <c r="C971" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D971" t="str">
+        <v>בפאנל העזרים - כותרת קטגוריית ATIS לא מיושרת/במרווח זהה לשאר הקטגוריות</v>
+      </c>
+      <c r="E971" t="str">
+        <v/>
+      </c>
+      <c r="F971" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F970"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F971"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F971"/>
+  <dimension ref="A1:F997"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -19827,9 +19827,529 @@
         <v/>
       </c>
     </row>
+    <row r="972">
+      <c r="A972" t="str">
+        <v/>
+      </c>
+      <c r="B972" t="str">
+        <v>2026-09-10 14:06</v>
+      </c>
+      <c r="C972" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D972" t="str">
+        <v>ניהול שדה - סרגל הכלים: להסתיר פקדים שאינם רלוונטיים בהקשר זה (הצג שמות הקפה, תלת מימד, מז"א)</v>
+      </c>
+      <c r="E972" t="str">
+        <v/>
+      </c>
+      <c r="F972" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" t="str">
+        <v/>
+      </c>
+      <c r="B973" t="str">
+        <v>2026-09-10 14:10</v>
+      </c>
+      <c r="C973" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D973" t="str">
+        <v>חלון ניהול רכבים - שדות התאריך יהיו רכיב בחירת תאריך ולא טקסט חופשי</v>
+      </c>
+      <c r="E973" t="str">
+        <v/>
+      </c>
+      <c r="F973" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="str">
+        <v/>
+      </c>
+      <c r="B974" t="str">
+        <v>2026-09-10 14:10</v>
+      </c>
+      <c r="C974" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D974" t="str">
+        <v>חלון ניהול רכבים - בהוספת רכב שדות השורה אינם באותו גובה</v>
+      </c>
+      <c r="E974" t="str">
+        <v/>
+      </c>
+      <c r="F974" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="str">
+        <v/>
+      </c>
+      <c r="B975" t="str">
+        <v>2026-09-10 14:10</v>
+      </c>
+      <c r="C975" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D975" t="str">
+        <v>חלון ניהול רכבים - להגדיל את החלון לכל גודל המסך</v>
+      </c>
+      <c r="E975" t="str">
+        <v/>
+      </c>
+      <c r="F975" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="str">
+        <v/>
+      </c>
+      <c r="B976" t="str">
+        <v>2026-09-10 14:15</v>
+      </c>
+      <c r="C976" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D976" t="str">
+        <v>ניהול שדה תעופה: פופאפ/תפריט שנפתח על אלמנט בטופס נפתח לא צמוד לאלמנט ויוצא מחוץ לתצוגה של החלון המרכזי</v>
+      </c>
+      <c r="E976" t="str">
+        <v/>
+      </c>
+      <c r="F976" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="str">
+        <v/>
+      </c>
+      <c r="B977" t="str">
+        <v>2026-09-10 15:16</v>
+      </c>
+      <c r="C977" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D977" t="str">
+        <v>קשירת מסלולים בין עמדות (תל נוף קרקע ↔ תל נוף אווירי) לא משתקפת הפוך בניהול - הקשירה צריכה להיות דו-כיוונית</v>
+      </c>
+      <c r="E977" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F977" t="str">
+        <v>ade277c - v1.0.171 (main)</v>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" t="str">
+        <v/>
+      </c>
+      <c r="B978" t="str">
+        <v>2026-09-10 15:16</v>
+      </c>
+      <c r="C978" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D978" t="str">
+        <v>מסלול שנסגר בעמדת תל נוף אווירי לא מוצג כסגור בעמדת תל נוף קרקעי</v>
+      </c>
+      <c r="E978" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F978" t="str">
+        <v>ade277c - v1.0.171 (main)</v>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="str">
+        <v/>
+      </c>
+      <c r="B979" t="str">
+        <v>2026-09-11 17:36</v>
+      </c>
+      <c r="C979" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D979" t="str">
+        <v>כלל קבע ב-CLAUDE.md ובסקיל: בסוף כל עבודה לקמט ולדחוף לגיט אוטומטית, בלי לחכות לאישור המשתמש</v>
+      </c>
+      <c r="E979" t="str">
+        <v/>
+      </c>
+      <c r="F979" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" t="str">
+        <v/>
+      </c>
+      <c r="B980" t="str">
+        <v>2026-09-12 08:40</v>
+      </c>
+      <c r="C980" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D980" t="str">
+        <v>פאנל האלמנטים בעמדת שדה: תג השמישות בתפריט השמאלי חייב לשקף את מה שנקבע ב-POPUP של האלמנט על המפה (ה-POPUP הוא הקובע)</v>
+      </c>
+      <c r="E980" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F980" t="str">
+        <v>387aa1e - v1.0.173 (main)</v>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="str">
+        <v/>
+      </c>
+      <c r="B981" t="str">
+        <v>2026-09-12 08:40</v>
+      </c>
+      <c r="C981" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D981" t="str">
+        <v>פאנל האלמנטים: לחיצה על האייקון שמשמאל לטקסט תחליף את סטטוס האלמנט (פתוח/סגור/מהבהב) לפי הסטטוסים שהוגדרו לאלמנט</v>
+      </c>
+      <c r="E981" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F981" t="str">
+        <v>387aa1e - v1.0.173 (main)</v>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" t="str">
+        <v/>
+      </c>
+      <c r="B982" t="str">
+        <v>2026-09-12 08:40</v>
+      </c>
+      <c r="C982" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D982" t="str">
+        <v>פאנל האלמנטים: "מוצג על מפה" יסומן ב-V / ללא V במקום התצוגה הנוכחית</v>
+      </c>
+      <c r="E982" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F982" t="str">
+        <v>387aa1e - v1.0.173 (main)</v>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" t="str">
+        <v/>
+      </c>
+      <c r="B983" t="str">
+        <v>2026-09-12 08:40</v>
+      </c>
+      <c r="C983" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D983" t="str">
+        <v>ניהול שדה תעופה: פתיחת טבלת אלמנטים מלאה עם כל הסטטוסים והכשירויות ויכולת פילטור על כל העמודות</v>
+      </c>
+      <c r="E983" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F983" t="str">
+        <v>387aa1e - v1.0.173 (main)</v>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="str">
+        <v/>
+      </c>
+      <c r="B984" t="str">
+        <v>2026-09-12 09:42</v>
+      </c>
+      <c r="C984" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D984" t="str">
+        <v>בניהול שדה תעופה: שינוי שם הטבלה "ניהול רכבים" ל"ניהול נהגים"</v>
+      </c>
+      <c r="E984" t="str">
+        <v/>
+      </c>
+      <c r="F984" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" t="str">
+        <v/>
+      </c>
+      <c r="B985" t="str">
+        <v>2026-09-12 09:42</v>
+      </c>
+      <c r="C985" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D985" t="str">
+        <v>ניהול נסיעות: טבלה חדשה - רכב, נהג, סוג רכב, סוג נסיעה, אייקון ניתן לשינוי, תאריך/שעת יציאה משוערים, מוצא, יעד, תחנות ביניים, סטטוס, נתיב מוצע/נבחר, הערה, טלפונים, מבקש, נלווים, אישור הסתובבות בבסיס</v>
+      </c>
+      <c r="E985" t="str">
+        <v/>
+      </c>
+      <c r="F985" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" t="str">
+        <v/>
+      </c>
+      <c r="B986" t="str">
+        <v>2026-09-12 09:42</v>
+      </c>
+      <c r="C986" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D986" t="str">
+        <v>ניהול נסיעות: הצגת הרכב ליד נקודת המוצא 10 דק לפני, עם התראה מתפרצת על תחילת הנסיעה</v>
+      </c>
+      <c r="E986" t="str">
+        <v/>
+      </c>
+      <c r="F986" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" t="str">
+        <v/>
+      </c>
+      <c r="B987" t="str">
+        <v>2026-09-12 09:42</v>
+      </c>
+      <c r="C987" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D987" t="str">
+        <v>ניהול נסיעות: שינוי סטטוס נסיעה מהמגדל כשהנהג מתקשר להתחיל נסיעה</v>
+      </c>
+      <c r="E987" t="str">
+        <v/>
+      </c>
+      <c r="F987" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" t="str">
+        <v/>
+      </c>
+      <c r="B988" t="str">
+        <v>2026-09-12 09:42</v>
+      </c>
+      <c r="C988" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D988" t="str">
+        <v>ניהול נסיעות: אישור נסיעה ע"י הנהג באפליקציה שלו -&gt; התראה מתפרצת במגדל</v>
+      </c>
+      <c r="E988" t="str">
+        <v/>
+      </c>
+      <c r="F988" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" t="str">
+        <v/>
+      </c>
+      <c r="B989" t="str">
+        <v>2026-09-12 09:42</v>
+      </c>
+      <c r="C989" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D989" t="str">
+        <v>ניהול נסיעות: עדכון זמן יציאה/תחנות ע"י הנהג באפליקציה -&gt; התראה לאישור נוסף של המגדל</v>
+      </c>
+      <c r="E989" t="str">
+        <v/>
+      </c>
+      <c r="F989" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" t="str">
+        <v/>
+      </c>
+      <c r="B990" t="str">
+        <v>2026-09-12 11:40</v>
+      </c>
+      <c r="C990" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D990" t="str">
+        <v>ניהול נסיעות: רשימת הנסיעות תתפרס על כל רוחב החלון כתצוגת ברירת מחדל; הטופס המלא נפתח רק בנסיעה חדשה או בעדכון</v>
+      </c>
+      <c r="E990" t="str">
+        <v/>
+      </c>
+      <c r="F990" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" t="str">
+        <v/>
+      </c>
+      <c r="B991" t="str">
+        <v>2026-09-12 11:40</v>
+      </c>
+      <c r="C991" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D991" t="str">
+        <v>ניהול נסיעות: בחישוב נתיב המשתמש חייב לבחור במפורש איזה נתיב מאושר לנהג (אין בחירה אוטומטית, ולא כמה נתיבים מסומנים בו-זמנית)</v>
+      </c>
+      <c r="E991" t="str">
+        <v/>
+      </c>
+      <c r="F991" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="str">
+        <v/>
+      </c>
+      <c r="B992" t="str">
+        <v>2026-09-12 12:15</v>
+      </c>
+      <c r="C992" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D992" t="str">
+        <v>ניהול נסיעות: לחיצה על "עדכן" פותחת טופס ריק במקום טופס עם נתוני הנסיעה</v>
+      </c>
+      <c r="E992" t="str">
+        <v/>
+      </c>
+      <c r="F992" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" t="str">
+        <v/>
+      </c>
+      <c r="B993" t="str">
+        <v>2026-09-12 12:15</v>
+      </c>
+      <c r="C993" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D993" t="str">
+        <v>ניהול נסיעות: שכפול נסיעה בודדת</v>
+      </c>
+      <c r="E993" t="str">
+        <v/>
+      </c>
+      <c r="F993" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="str">
+        <v/>
+      </c>
+      <c r="B994" t="str">
+        <v>2026-09-12 12:15</v>
+      </c>
+      <c r="C994" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D994" t="str">
+        <v>ניהול נסיעות: שכפול קבוצתי - שכפול כמה נסיעות שנבחרו יחד</v>
+      </c>
+      <c r="E994" t="str">
+        <v/>
+      </c>
+      <c r="F994" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="str">
+        <v/>
+      </c>
+      <c r="B995" t="str">
+        <v>2026-09-12 17:39</v>
+      </c>
+      <c r="C995" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D995" t="str">
+        <v>ניהול נסיעות: חישוב הנתיב אינו מתחשב בתחנות הביניים - הנתיב מחושב מהמוצא ליעד בלבד</v>
+      </c>
+      <c r="E995" t="str">
+        <v/>
+      </c>
+      <c r="F995" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" t="str">
+        <v/>
+      </c>
+      <c r="B996" t="str">
+        <v>2026-09-12 17:39</v>
+      </c>
+      <c r="C996" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D996" t="str">
+        <v>ניהול נסיעות: כל שינוי במוצא / יעד / תחנות ביניים יגרום לחישוב נתיב מחדש אוטומטית</v>
+      </c>
+      <c r="E996" t="str">
+        <v/>
+      </c>
+      <c r="F996" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" t="str">
+        <v/>
+      </c>
+      <c r="B997" t="str">
+        <v>2026-09-12 17:40</v>
+      </c>
+      <c r="C997" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D997" t="str">
+        <v>ניהול שדה: לחיצה על הריבוע ברשימת האלמנטים לא פותחת את בורר הסטטוס (סגור/מהבהב לפי הטופס) - הפופאפ לא נפתח או מוסתר</v>
+      </c>
+      <c r="E997" t="str">
+        <v/>
+      </c>
+      <c r="F997" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F971"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F997"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F997"/>
+  <dimension ref="A1:F1001"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -20347,9 +20347,89 @@
         <v/>
       </c>
     </row>
+    <row r="998">
+      <c r="A998" t="str">
+        <v/>
+      </c>
+      <c r="B998" t="str">
+        <v>2026-09-12 19:13</v>
+      </c>
+      <c r="C998" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D998" t="str">
+        <v>ניהול שדה: ברשימת האלמנטים להציג את הסטטוס התפעולי שנבחר (סגור/מהבהב) ולא ריבוע ריק</v>
+      </c>
+      <c r="E998" t="str">
+        <v/>
+      </c>
+      <c r="F998" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="str">
+        <v/>
+      </c>
+      <c r="B999" t="str">
+        <v>2026-09-12 19:13</v>
+      </c>
+      <c r="C999" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D999" t="str">
+        <v>התראת "תחילת נסיעה" - לאפשר לגרור את החלון למקום אחר על המסך</v>
+      </c>
+      <c r="E999" t="str">
+        <v/>
+      </c>
+      <c r="F999" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="str">
+        <v/>
+      </c>
+      <c r="B1000" t="str">
+        <v>2026-09-12 19:13</v>
+      </c>
+      <c r="C1000" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1000" t="str">
+        <v>התראת "תחילת נסיעה" - לאפשר לעגן אותה בקונטיינר החלונות</v>
+      </c>
+      <c r="E1000" t="str">
+        <v/>
+      </c>
+      <c r="F1000" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="str">
+        <v/>
+      </c>
+      <c r="B1001" t="str">
+        <v>2026-09-12 19:14</v>
+      </c>
+      <c r="C1001" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1001" t="str">
+        <v>טופס יצירת/עדכון נסיעה - נמרח על כל המסך וגדול מדי; להקטין לגודל שאפשר לעבוד איתו</v>
+      </c>
+      <c r="E1001" t="str">
+        <v/>
+      </c>
+      <c r="F1001" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F997"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1001"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1001"/>
+  <dimension ref="A1:F1003"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -20427,9 +20427,49 @@
         <v/>
       </c>
     </row>
+    <row r="1002">
+      <c r="A1002" t="str">
+        <v/>
+      </c>
+      <c r="B1002" t="str">
+        <v>2026-09-12 19:33</v>
+      </c>
+      <c r="C1002" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1002" t="str">
+        <v>התראת נסיעה - בגרירה החלון לא נוחת במיקום העכבר/העט</v>
+      </c>
+      <c r="E1002" t="str">
+        <v/>
+      </c>
+      <c r="F1002" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="str">
+        <v/>
+      </c>
+      <c r="B1003" t="str">
+        <v>2026-09-12 19:40</v>
+      </c>
+      <c r="C1003" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1003" t="str">
+        <v>ניהול שדה: בסרגל הכלים במצב מוקטן, אחרי סגירת החלון בצד מופיע רק "ציור" ואי אפשר להחזיר את שאר הכלים</v>
+      </c>
+      <c r="E1003" t="str">
+        <v/>
+      </c>
+      <c r="F1003" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1001"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1003"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1003"/>
+  <dimension ref="A1:F1006"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -20467,9 +20467,69 @@
         <v/>
       </c>
     </row>
+    <row r="1004">
+      <c r="A1004" t="str">
+        <v/>
+      </c>
+      <c r="B1004" t="str">
+        <v>2026-09-13 10:02</v>
+      </c>
+      <c r="C1004" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1004" t="str">
+        <v>אלמנט על מפת השדה - להוריד את צבע הסוג ולהשאיר רק את הסטטוס; אלמנט בלי סטטוס יציג "אין סטטוס"</v>
+      </c>
+      <c r="E1004" t="str">
+        <v/>
+      </c>
+      <c r="F1004" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="str">
+        <v/>
+      </c>
+      <c r="B1005" t="str">
+        <v>2026-09-13 10:07</v>
+      </c>
+      <c r="C1005" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1005" t="str">
+        <v>הרשאות לאפליקציית DRIVER - רק משתמש מורשה יכול לפתוח את DRIVER</v>
+      </c>
+      <c r="E1005" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1005" t="str">
+        <v>682c57f v1.0.184</v>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="str">
+        <v/>
+      </c>
+      <c r="B1006" t="str">
+        <v>2026-09-13 10:07</v>
+      </c>
+      <c r="C1006" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1006" t="str">
+        <v>DRIVER מציג רק את הנסיעות של הנהג המחובר, לפי זיהוי נהג במספר תעודת זהות</v>
+      </c>
+      <c r="E1006" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1006" t="str">
+        <v>682c57f v1.0.184</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1003"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1006"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1006"/>
+  <dimension ref="A1:F1008"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -20527,9 +20527,49 @@
         <v>682c57f v1.0.184</v>
       </c>
     </row>
+    <row r="1007">
+      <c r="A1007" t="str">
+        <v/>
+      </c>
+      <c r="B1007" t="str">
+        <v>2026-09-13 10:41</v>
+      </c>
+      <c r="C1007" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1007" t="str">
+        <v>מסך הניהול במיראז' - לבחור אפליקציה SKY-KING DRIVER כהרשאה נפרדת מ-SKY-KING</v>
+      </c>
+      <c r="E1007" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1007" t="str">
+        <v>86578bf v1.0.186</v>
+      </c>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="str">
+        <v/>
+      </c>
+      <c r="B1008" t="str">
+        <v>2026-09-13 10:41</v>
+      </c>
+      <c r="C1008" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1008" t="str">
+        <v>הרשאת SKY-KING DRIVER במיראז' - בחירת הבסיס/ים שהנהג מורשה אליהם</v>
+      </c>
+      <c r="E1008" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1008" t="str">
+        <v>86578bf v1.0.186</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1006"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1008"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1008"/>
+  <dimension ref="A1:F1030"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -20567,9 +20567,449 @@
         <v>86578bf v1.0.186</v>
       </c>
     </row>
+    <row r="1009">
+      <c r="A1009" t="str">
+        <v/>
+      </c>
+      <c r="B1009" t="str">
+        <v>2026-09-13 18:56</v>
+      </c>
+      <c r="C1009" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1009" t="str">
+        <v>DRIVER - מסך כניסה עם אנימציה של אמבולנס ומשאית נכנסים</v>
+      </c>
+      <c r="E1009" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1009" t="str">
+        <v>956d808 v1.0.188</v>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="str">
+        <v/>
+      </c>
+      <c r="B1010" t="str">
+        <v>2026-09-13 18:56</v>
+      </c>
+      <c r="C1010" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1010" t="str">
+        <v>DRIVER - אחרי כניסה ברכה לפי השעה (בוקר טוב / ערב טוב) ושם המשתמש</v>
+      </c>
+      <c r="E1010" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1010" t="str">
+        <v>956d808 v1.0.188</v>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="str">
+        <v/>
+      </c>
+      <c r="B1011" t="str">
+        <v>2026-09-13 18:56</v>
+      </c>
+      <c r="C1011" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1011" t="str">
+        <v>DRIVER - נהג עם כמה בסיסים בוחר בסיס; ברירת מחדל הבסיס הקרוב לפי GPS של הטלפון, ואפשר לבחור אחר</v>
+      </c>
+      <c r="E1011" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1011" t="str">
+        <v>956d808 v1.0.188</v>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="str">
+        <v/>
+      </c>
+      <c r="B1012" t="str">
+        <v>2026-09-13 18:56</v>
+      </c>
+      <c r="C1012" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1012" t="str">
+        <v>DRIVER - טאב נסיעות מאושרות, ממוין מהמוקדם למאוחר</v>
+      </c>
+      <c r="E1012" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1012" t="str">
+        <v>956d808 v1.0.188</v>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="str">
+        <v/>
+      </c>
+      <c r="B1013" t="str">
+        <v>2026-09-13 18:56</v>
+      </c>
+      <c r="C1013" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1013" t="str">
+        <v>DRIVER - טאב בקשות ממתינות, מקובץ לפי ממתין לאישור / נדחה, ממוין לפי זמן</v>
+      </c>
+      <c r="E1013" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1013" t="str">
+        <v>956d808 v1.0.188</v>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="str">
+        <v/>
+      </c>
+      <c r="B1014" t="str">
+        <v>2026-09-13 18:56</v>
+      </c>
+      <c r="C1014" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1014" t="str">
+        <v>DRIVER - טאב היסטוריית נסיעות (רק נסיעות שבוצעו)</v>
+      </c>
+      <c r="E1014" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1014" t="str">
+        <v>956d808 v1.0.188</v>
+      </c>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="str">
+        <v/>
+      </c>
+      <c r="B1015" t="str">
+        <v>2026-09-13 18:56</v>
+      </c>
+      <c r="C1015" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1015" t="str">
+        <v>DRIVER - כפתור בקשה חדשה שפותח טופס נסיעה כמו באתר, בלי חלקי האישור</v>
+      </c>
+      <c r="E1015" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1015" t="str">
+        <v>956d808 v1.0.188</v>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="str">
+        <v/>
+      </c>
+      <c r="B1016" t="str">
+        <v>2026-09-13 19:39</v>
+      </c>
+      <c r="C1016" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1016" t="str">
+        <v>DRIVER - כל כניסה חדשה לכתובת /driver מציגה מסך LOGIN (לא נשארים מחוברים)</v>
+      </c>
+      <c r="E1016" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1016" t="str">
+        <v>28aae91 v1.0.189</v>
+      </c>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="str">
+        <v/>
+      </c>
+      <c r="B1017" t="str">
+        <v>2026-09-13 19:44</v>
+      </c>
+      <c r="C1017" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1017" t="str">
+        <v>חלון ניהול נסיעות - אישור נסיעה ישירות מהרשימה בחלון, בלי לפתוח את הטופס</v>
+      </c>
+      <c r="E1017" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1017" t="str">
+        <v>42cc6a7 v1.0.191</v>
+      </c>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="str">
+        <v/>
+      </c>
+      <c r="B1018" t="str">
+        <v>2026-09-13 19:44</v>
+      </c>
+      <c r="C1018" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1018" t="str">
+        <v>חלון ניהול נסיעות - קיבוץ לפי כל אחת מהעמודות; ברירת מחדל קיבוץ לפי סטטוס ומיון לפי זמן</v>
+      </c>
+      <c r="E1018" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1018" t="str">
+        <v>42cc6a7 v1.0.191</v>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="str">
+        <v/>
+      </c>
+      <c r="B1019" t="str">
+        <v>2026-09-13 19:56</v>
+      </c>
+      <c r="C1019" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1019" t="str">
+        <v>DRIVER - כפתור "הפעל נסיעה" על נסיעה מאושרת, רק מחצי שעה לפני עד חצי שעה אחרי; מחוץ לחלון התראה שנדרש לעדכן</v>
+      </c>
+      <c r="E1019" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1019" t="str">
+        <v>2878614 v1.0.193</v>
+      </c>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="str">
+        <v/>
+      </c>
+      <c r="B1020" t="str">
+        <v>2026-09-13 19:56</v>
+      </c>
+      <c r="C1020" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1020" t="str">
+        <v>עדכון נסיעה מהנהג - התראה בעמדת האישורים במגדל, והסטטוס חוזר לממתין בעקבות עדכון X (גם אם אושר)</v>
+      </c>
+      <c r="E1020" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1020" t="str">
+        <v>2878614 v1.0.193</v>
+      </c>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="str">
+        <v/>
+      </c>
+      <c r="B1021" t="str">
+        <v>2026-09-13 20:00</v>
+      </c>
+      <c r="C1021" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1021" t="str">
+        <v>אנימציית רכבים: PLAY על רכב בניהול שדה מציג קו מקווקו אדום עד עצירת האנימציה, גם כשכל המסלולים בסרגל כבויים</v>
+      </c>
+      <c r="E1021" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1021" t="str">
+        <v>eb3ddce v1.0.192</v>
+      </c>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="str">
+        <v/>
+      </c>
+      <c r="B1022" t="str">
+        <v>2026-09-13 20:17</v>
+      </c>
+      <c r="C1022" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1022" t="str">
+        <v>אחרי שהמגדל מאשר בקשת שינוי של נהג - באפליקציית הנהג הנסיעה לא עוברת לסטטוס "מאושר"</v>
+      </c>
+      <c r="E1022" t="str">
+        <v/>
+      </c>
+      <c r="F1022" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="str">
+        <v/>
+      </c>
+      <c r="B1023" t="str">
+        <v>2026-09-13 20:17</v>
+      </c>
+      <c r="C1023" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1023" t="str">
+        <v>בקשת שינוי של נהג - ההערה שמתארת את מהות השינוי אינה מדויקת</v>
+      </c>
+      <c r="E1023" t="str">
+        <v/>
+      </c>
+      <c r="F1023" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="str">
+        <v/>
+      </c>
+      <c r="B1024" t="str">
+        <v>2026-09-13 20:42</v>
+      </c>
+      <c r="C1024" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1024" t="str">
+        <v>אפליקציית נהג - אחרי הפעלת נסיעה לפתוח מפה עם הנתיב ואלמנטים רלוונטיים לנתיב (רמזורים דולק/כבוי, מחסומים וכו')</v>
+      </c>
+      <c r="E1024" t="str">
+        <v/>
+      </c>
+      <c r="F1024" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="str">
+        <v/>
+      </c>
+      <c r="B1025" t="str">
+        <v>2026-09-13 20:42</v>
+      </c>
+      <c r="C1025" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1025" t="str">
+        <v>אפליקציית נהג - התרעה בהתקרבות למסלול הסעה, מסלול טיסה או אלמנט</v>
+      </c>
+      <c r="E1025" t="str">
+        <v/>
+      </c>
+      <c r="F1025" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="str">
+        <v/>
+      </c>
+      <c r="B1026" t="str">
+        <v>2026-09-13 20:42</v>
+      </c>
+      <c r="C1026" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1026" t="str">
+        <v>אפליקציית נהג - שידור נ"צ חי חזרה לאפליקציה הראשית במהלך נסיעה</v>
+      </c>
+      <c r="E1026" t="str">
+        <v/>
+      </c>
+      <c r="F1026" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="str">
+        <v/>
+      </c>
+      <c r="B1027" t="str">
+        <v>2026-09-13 20:42</v>
+      </c>
+      <c r="C1027" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1027" t="str">
+        <v>אפליקציה ראשית - הצגת הרכב נוסע על המפה לפי הנ"צ המשודר</v>
+      </c>
+      <c r="E1027" t="str">
+        <v/>
+      </c>
+      <c r="F1027" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="str">
+        <v/>
+      </c>
+      <c r="B1028" t="str">
+        <v>2026-09-13 20:42</v>
+      </c>
+      <c r="C1028" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1028" t="str">
+        <v>אפליקציה ראשית - התרעה כשרכב סוטה 200 מ' מהמסלול המתוכנן או מתקרב לאלמנט שסוגר את הנתיב</v>
+      </c>
+      <c r="E1028" t="str">
+        <v/>
+      </c>
+      <c r="F1028" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="str">
+        <v/>
+      </c>
+      <c r="B1029" t="str">
+        <v>2026-09-13 21:24</v>
+      </c>
+      <c r="C1029" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1029" t="str">
+        <v>שירות "טבלאות מתצוגה" בדסק משימה - בהגדרת הדסק בניהול עמדה לבחור אילו טבלאות מתפריט תצוגה ייפתחו (אלמנטים, הסעות, קונטיינרים, נהגים, כמויות, הודעות)</v>
+      </c>
+      <c r="E1029" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1029" t="str">
+        <v>1b4009e (v1.0.198)</v>
+      </c>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="str">
+        <v/>
+      </c>
+      <c r="B1030" t="str">
+        <v>2026-09-13 21:43</v>
+      </c>
+      <c r="C1030" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1030" t="str">
+        <v>ניהול נסיעות: הלוח אינו מתעדכן בזמן אמת - נדרש לסגור ולפתוח את החלון כדי לראות שינויים</v>
+      </c>
+      <c r="E1030" t="str">
+        <v/>
+      </c>
+      <c r="F1030" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1008"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1030"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1030"/>
+  <dimension ref="A1:F1031"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -21007,9 +21007,29 @@
         <v/>
       </c>
     </row>
+    <row r="1031">
+      <c r="A1031" t="str">
+        <v/>
+      </c>
+      <c r="B1031" t="str">
+        <v>2026-09-13 22:17</v>
+      </c>
+      <c r="C1031" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1031" t="str">
+        <v>טבלאות מתצוגה בדסק משימה - בהגדרת העמדה לבחור לכל טבלה לפי איזו עמדה היא מוצגת (בנוסף לבחירת הטבלה)</v>
+      </c>
+      <c r="E1031" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1031" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1030"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1031"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1031"/>
+  <dimension ref="A1:F1047"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -20472,13 +20472,13 @@
         <v/>
       </c>
       <c r="B1004" t="str">
-        <v>2026-09-13 10:02</v>
+        <v>2026-09-13 00:09</v>
       </c>
       <c r="C1004" t="str">
         <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1004" t="str">
-        <v>אלמנט על מפת השדה - להוריד את צבע הסוג ולהשאיר רק את הסטטוס; אלמנט בלי סטטוס יציג "אין סטטוס"</v>
+        <v>אפליקציית הנהג: סמלי האלמנטים כמו באפליקציה הראשית - כולל האנימציה והמצבים</v>
       </c>
       <c r="E1004" t="str">
         <v/>
@@ -20492,19 +20492,19 @@
         <v/>
       </c>
       <c r="B1005" t="str">
-        <v>2026-09-13 10:07</v>
+        <v>2026-09-13 10:02</v>
       </c>
       <c r="C1005" t="str">
-        <v>תכולה חדשה</v>
+        <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1005" t="str">
-        <v>הרשאות לאפליקציית DRIVER - רק משתמש מורשה יכול לפתוח את DRIVER</v>
+        <v>אלמנט על מפת השדה - להוריד את צבע הסוג ולהשאיר רק את הסטטוס; אלמנט בלי סטטוס יציג "אין סטטוס"</v>
       </c>
       <c r="E1005" t="str">
-        <v>כן</v>
+        <v/>
       </c>
       <c r="F1005" t="str">
-        <v>682c57f v1.0.184</v>
+        <v/>
       </c>
     </row>
     <row r="1006">
@@ -20518,7 +20518,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1006" t="str">
-        <v>DRIVER מציג רק את הנסיעות של הנהג המחובר, לפי זיהוי נהג במספר תעודת זהות</v>
+        <v>הרשאות לאפליקציית DRIVER - רק משתמש מורשה יכול לפתוח את DRIVER</v>
       </c>
       <c r="E1006" t="str">
         <v>כן</v>
@@ -20532,19 +20532,19 @@
         <v/>
       </c>
       <c r="B1007" t="str">
-        <v>2026-09-13 10:41</v>
+        <v>2026-09-13 10:07</v>
       </c>
       <c r="C1007" t="str">
-        <v>שיפור לתכולה קיימת</v>
+        <v>תכולה חדשה</v>
       </c>
       <c r="D1007" t="str">
-        <v>מסך הניהול במיראז' - לבחור אפליקציה SKY-KING DRIVER כהרשאה נפרדת מ-SKY-KING</v>
+        <v>DRIVER מציג רק את הנסיעות של הנהג המחובר, לפי זיהוי נהג במספר תעודת זהות</v>
       </c>
       <c r="E1007" t="str">
         <v>כן</v>
       </c>
       <c r="F1007" t="str">
-        <v>86578bf v1.0.186</v>
+        <v>682c57f v1.0.184</v>
       </c>
     </row>
     <row r="1008">
@@ -20555,10 +20555,10 @@
         <v>2026-09-13 10:41</v>
       </c>
       <c r="C1008" t="str">
-        <v>תכולה חדשה</v>
+        <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1008" t="str">
-        <v>הרשאת SKY-KING DRIVER במיראז' - בחירת הבסיס/ים שהנהג מורשה אליהם</v>
+        <v>מסך הניהול במיראז' - לבחור אפליקציה SKY-KING DRIVER כהרשאה נפרדת מ-SKY-KING</v>
       </c>
       <c r="E1008" t="str">
         <v>כן</v>
@@ -20572,19 +20572,19 @@
         <v/>
       </c>
       <c r="B1009" t="str">
-        <v>2026-09-13 18:56</v>
+        <v>2026-09-13 10:41</v>
       </c>
       <c r="C1009" t="str">
-        <v>שיפור לתכולה קיימת</v>
+        <v>תכולה חדשה</v>
       </c>
       <c r="D1009" t="str">
-        <v>DRIVER - מסך כניסה עם אנימציה של אמבולנס ומשאית נכנסים</v>
+        <v>הרשאת SKY-KING DRIVER במיראז' - בחירת הבסיס/ים שהנהג מורשה אליהם</v>
       </c>
       <c r="E1009" t="str">
         <v>כן</v>
       </c>
       <c r="F1009" t="str">
-        <v>956d808 v1.0.188</v>
+        <v>86578bf v1.0.186</v>
       </c>
     </row>
     <row r="1010">
@@ -20595,10 +20595,10 @@
         <v>2026-09-13 18:56</v>
       </c>
       <c r="C1010" t="str">
-        <v>תכולה חדשה</v>
+        <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1010" t="str">
-        <v>DRIVER - אחרי כניסה ברכה לפי השעה (בוקר טוב / ערב טוב) ושם המשתמש</v>
+        <v>DRIVER - מסך כניסה עם אנימציה של אמבולנס ומשאית נכנסים</v>
       </c>
       <c r="E1010" t="str">
         <v>כן</v>
@@ -20618,7 +20618,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1011" t="str">
-        <v>DRIVER - נהג עם כמה בסיסים בוחר בסיס; ברירת מחדל הבסיס הקרוב לפי GPS של הטלפון, ואפשר לבחור אחר</v>
+        <v>DRIVER - אחרי כניסה ברכה לפי השעה (בוקר טוב / ערב טוב) ושם המשתמש</v>
       </c>
       <c r="E1011" t="str">
         <v>כן</v>
@@ -20638,7 +20638,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1012" t="str">
-        <v>DRIVER - טאב נסיעות מאושרות, ממוין מהמוקדם למאוחר</v>
+        <v>DRIVER - נהג עם כמה בסיסים בוחר בסיס; ברירת מחדל הבסיס הקרוב לפי GPS של הטלפון, ואפשר לבחור אחר</v>
       </c>
       <c r="E1012" t="str">
         <v>כן</v>
@@ -20658,7 +20658,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1013" t="str">
-        <v>DRIVER - טאב בקשות ממתינות, מקובץ לפי ממתין לאישור / נדחה, ממוין לפי זמן</v>
+        <v>DRIVER - טאב נסיעות מאושרות, ממוין מהמוקדם למאוחר</v>
       </c>
       <c r="E1013" t="str">
         <v>כן</v>
@@ -20678,7 +20678,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1014" t="str">
-        <v>DRIVER - טאב היסטוריית נסיעות (רק נסיעות שבוצעו)</v>
+        <v>DRIVER - טאב בקשות ממתינות, מקובץ לפי ממתין לאישור / נדחה, ממוין לפי זמן</v>
       </c>
       <c r="E1014" t="str">
         <v>כן</v>
@@ -20698,7 +20698,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1015" t="str">
-        <v>DRIVER - כפתור בקשה חדשה שפותח טופס נסיעה כמו באתר, בלי חלקי האישור</v>
+        <v>DRIVER - טאב היסטוריית נסיעות (רק נסיעות שבוצעו)</v>
       </c>
       <c r="E1015" t="str">
         <v>כן</v>
@@ -20712,19 +20712,19 @@
         <v/>
       </c>
       <c r="B1016" t="str">
-        <v>2026-09-13 19:39</v>
+        <v>2026-09-13 18:56</v>
       </c>
       <c r="C1016" t="str">
-        <v>שיפור לתכולה קיימת</v>
+        <v>תכולה חדשה</v>
       </c>
       <c r="D1016" t="str">
-        <v>DRIVER - כל כניסה חדשה לכתובת /driver מציגה מסך LOGIN (לא נשארים מחוברים)</v>
+        <v>DRIVER - כפתור בקשה חדשה שפותח טופס נסיעה כמו באתר, בלי חלקי האישור</v>
       </c>
       <c r="E1016" t="str">
         <v>כן</v>
       </c>
       <c r="F1016" t="str">
-        <v>28aae91 v1.0.189</v>
+        <v>956d808 v1.0.188</v>
       </c>
     </row>
     <row r="1017">
@@ -20732,19 +20732,19 @@
         <v/>
       </c>
       <c r="B1017" t="str">
-        <v>2026-09-13 19:44</v>
+        <v>2026-09-13 19:39</v>
       </c>
       <c r="C1017" t="str">
         <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1017" t="str">
-        <v>חלון ניהול נסיעות - אישור נסיעה ישירות מהרשימה בחלון, בלי לפתוח את הטופס</v>
+        <v>DRIVER - כל כניסה חדשה לכתובת /driver מציגה מסך LOGIN (לא נשארים מחוברים)</v>
       </c>
       <c r="E1017" t="str">
         <v>כן</v>
       </c>
       <c r="F1017" t="str">
-        <v>42cc6a7 v1.0.191</v>
+        <v>28aae91 v1.0.189</v>
       </c>
     </row>
     <row r="1018">
@@ -20758,7 +20758,7 @@
         <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1018" t="str">
-        <v>חלון ניהול נסיעות - קיבוץ לפי כל אחת מהעמודות; ברירת מחדל קיבוץ לפי סטטוס ומיון לפי זמן</v>
+        <v>חלון ניהול נסיעות - אישור נסיעה ישירות מהרשימה בחלון, בלי לפתוח את הטופס</v>
       </c>
       <c r="E1018" t="str">
         <v>כן</v>
@@ -20772,19 +20772,19 @@
         <v/>
       </c>
       <c r="B1019" t="str">
-        <v>2026-09-13 19:56</v>
+        <v>2026-09-13 19:44</v>
       </c>
       <c r="C1019" t="str">
-        <v>תכולה חדשה</v>
+        <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1019" t="str">
-        <v>DRIVER - כפתור "הפעל נסיעה" על נסיעה מאושרת, רק מחצי שעה לפני עד חצי שעה אחרי; מחוץ לחלון התראה שנדרש לעדכן</v>
+        <v>חלון ניהול נסיעות - קיבוץ לפי כל אחת מהעמודות; ברירת מחדל קיבוץ לפי סטטוס ומיון לפי זמן</v>
       </c>
       <c r="E1019" t="str">
         <v>כן</v>
       </c>
       <c r="F1019" t="str">
-        <v>2878614 v1.0.193</v>
+        <v>42cc6a7 v1.0.191</v>
       </c>
     </row>
     <row r="1020">
@@ -20795,10 +20795,10 @@
         <v>2026-09-13 19:56</v>
       </c>
       <c r="C1020" t="str">
-        <v>שיפור לתכולה קיימת</v>
+        <v>תכולה חדשה</v>
       </c>
       <c r="D1020" t="str">
-        <v>עדכון נסיעה מהנהג - התראה בעמדת האישורים במגדל, והסטטוס חוזר לממתין בעקבות עדכון X (גם אם אושר)</v>
+        <v>DRIVER - כפתור "הפעל נסיעה" על נסיעה מאושרת, רק מחצי שעה לפני עד חצי שעה אחרי; מחוץ לחלון התראה שנדרש לעדכן</v>
       </c>
       <c r="E1020" t="str">
         <v>כן</v>
@@ -20812,19 +20812,19 @@
         <v/>
       </c>
       <c r="B1021" t="str">
-        <v>2026-09-13 20:00</v>
+        <v>2026-09-13 19:56</v>
       </c>
       <c r="C1021" t="str">
         <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1021" t="str">
-        <v>אנימציית רכבים: PLAY על רכב בניהול שדה מציג קו מקווקו אדום עד עצירת האנימציה, גם כשכל המסלולים בסרגל כבויים</v>
+        <v>עדכון נסיעה מהנהג - התראה בעמדת האישורים במגדל, והסטטוס חוזר לממתין בעקבות עדכון X (גם אם אושר)</v>
       </c>
       <c r="E1021" t="str">
         <v>כן</v>
       </c>
       <c r="F1021" t="str">
-        <v>eb3ddce v1.0.192</v>
+        <v>2878614 v1.0.193</v>
       </c>
     </row>
     <row r="1022">
@@ -20832,19 +20832,19 @@
         <v/>
       </c>
       <c r="B1022" t="str">
-        <v>2026-09-13 20:17</v>
+        <v>2026-09-13 20:00</v>
       </c>
       <c r="C1022" t="str">
-        <v>תקלה</v>
+        <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1022" t="str">
-        <v>אחרי שהמגדל מאשר בקשת שינוי של נהג - באפליקציית הנהג הנסיעה לא עוברת לסטטוס "מאושר"</v>
+        <v>אנימציית רכבים: PLAY על רכב בניהול שדה מציג קו מקווקו אדום עד עצירת האנימציה, גם כשכל המסלולים בסרגל כבויים</v>
       </c>
       <c r="E1022" t="str">
-        <v/>
+        <v>כן</v>
       </c>
       <c r="F1022" t="str">
-        <v/>
+        <v>eb3ddce v1.0.192</v>
       </c>
     </row>
     <row r="1023">
@@ -20858,7 +20858,7 @@
         <v>תקלה</v>
       </c>
       <c r="D1023" t="str">
-        <v>בקשת שינוי של נהג - ההערה שמתארת את מהות השינוי אינה מדויקת</v>
+        <v>אחרי שהמגדל מאשר בקשת שינוי של נהג - באפליקציית הנהג הנסיעה לא עוברת לסטטוס "מאושר"</v>
       </c>
       <c r="E1023" t="str">
         <v/>
@@ -20872,13 +20872,13 @@
         <v/>
       </c>
       <c r="B1024" t="str">
-        <v>2026-09-13 20:42</v>
+        <v>2026-09-13 20:17</v>
       </c>
       <c r="C1024" t="str">
-        <v>תכולה חדשה</v>
+        <v>תקלה</v>
       </c>
       <c r="D1024" t="str">
-        <v>אפליקציית נהג - אחרי הפעלת נסיעה לפתוח מפה עם הנתיב ואלמנטים רלוונטיים לנתיב (רמזורים דולק/כבוי, מחסומים וכו')</v>
+        <v>בקשת שינוי של נהג - ההערה שמתארת את מהות השינוי אינה מדויקת</v>
       </c>
       <c r="E1024" t="str">
         <v/>
@@ -20898,7 +20898,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1025" t="str">
-        <v>אפליקציית נהג - התרעה בהתקרבות למסלול הסעה, מסלול טיסה או אלמנט</v>
+        <v>אפליקציית נהג - אחרי הפעלת נסיעה לפתוח מפה עם הנתיב ואלמנטים רלוונטיים לנתיב (רמזורים דולק/כבוי, מחסומים וכו')</v>
       </c>
       <c r="E1025" t="str">
         <v/>
@@ -20918,7 +20918,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1026" t="str">
-        <v>אפליקציית נהג - שידור נ"צ חי חזרה לאפליקציה הראשית במהלך נסיעה</v>
+        <v>אפליקציית נהג - התרעה בהתקרבות למסלול הסעה, מסלול טיסה או אלמנט</v>
       </c>
       <c r="E1026" t="str">
         <v/>
@@ -20938,7 +20938,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1027" t="str">
-        <v>אפליקציה ראשית - הצגת הרכב נוסע על המפה לפי הנ"צ המשודר</v>
+        <v>אפליקציית נהג - שידור נ"צ חי חזרה לאפליקציה הראשית במהלך נסיעה</v>
       </c>
       <c r="E1027" t="str">
         <v/>
@@ -20958,7 +20958,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1028" t="str">
-        <v>אפליקציה ראשית - התרעה כשרכב סוטה 200 מ' מהמסלול המתוכנן או מתקרב לאלמנט שסוגר את הנתיב</v>
+        <v>אפליקציה ראשית - הצגת הרכב נוסע על המפה לפי הנ"צ המשודר</v>
       </c>
       <c r="E1028" t="str">
         <v/>
@@ -20972,19 +20972,19 @@
         <v/>
       </c>
       <c r="B1029" t="str">
-        <v>2026-09-13 21:24</v>
+        <v>2026-09-13 20:42</v>
       </c>
       <c r="C1029" t="str">
         <v>תכולה חדשה</v>
       </c>
       <c r="D1029" t="str">
-        <v>שירות "טבלאות מתצוגה" בדסק משימה - בהגדרת הדסק בניהול עמדה לבחור אילו טבלאות מתפריט תצוגה ייפתחו (אלמנטים, הסעות, קונטיינרים, נהגים, כמויות, הודעות)</v>
+        <v>אפליקציה ראשית - התרעה כשרכב סוטה 200 מ' מהמסלול המתוכנן או מתקרב לאלמנט שסוגר את הנתיב</v>
       </c>
       <c r="E1029" t="str">
-        <v>כן</v>
+        <v/>
       </c>
       <c r="F1029" t="str">
-        <v>1b4009e (v1.0.198)</v>
+        <v/>
       </c>
     </row>
     <row r="1030">
@@ -20992,19 +20992,19 @@
         <v/>
       </c>
       <c r="B1030" t="str">
-        <v>2026-09-13 21:43</v>
+        <v>2026-09-13 21:24</v>
       </c>
       <c r="C1030" t="str">
-        <v>תקלה</v>
+        <v>תכולה חדשה</v>
       </c>
       <c r="D1030" t="str">
-        <v>ניהול נסיעות: הלוח אינו מתעדכן בזמן אמת - נדרש לסגור ולפתוח את החלון כדי לראות שינויים</v>
+        <v>שירות "טבלאות מתצוגה" בדסק משימה - בהגדרת הדסק בניהול עמדה לבחור אילו טבלאות מתפריט תצוגה ייפתחו (אלמנטים, הסעות, קונטיינרים, נהגים, כמויות, הודעות)</v>
       </c>
       <c r="E1030" t="str">
-        <v/>
+        <v>כן</v>
       </c>
       <c r="F1030" t="str">
-        <v/>
+        <v>1b4009e (v1.0.198)</v>
       </c>
     </row>
     <row r="1031">
@@ -21012,24 +21012,344 @@
         <v/>
       </c>
       <c r="B1031" t="str">
+        <v>2026-09-13 21:43</v>
+      </c>
+      <c r="C1031" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1031" t="str">
+        <v>ניהול נסיעות: הלוח אינו מתעדכן בזמן אמת - נדרש לסגור ולפתוח את החלון כדי לראות שינויים</v>
+      </c>
+      <c r="E1031" t="str">
+        <v/>
+      </c>
+      <c r="F1031" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="str">
+        <v/>
+      </c>
+      <c r="B1032" t="str">
         <v>2026-09-13 22:17</v>
       </c>
-      <c r="C1031" t="str">
-        <v>שיפור לתכולה קיימת</v>
-      </c>
-      <c r="D1031" t="str">
+      <c r="C1032" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1032" t="str">
         <v>טבלאות מתצוגה בדסק משימה - בהגדרת העמדה לבחור לכל טבלה לפי איזו עמדה היא מוצגת (בנוסף לבחירת הטבלה)</v>
       </c>
-      <c r="E1031" t="str">
-        <v>כן</v>
-      </c>
-      <c r="F1031" t="str">
-        <v/>
+      <c r="E1032" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1032" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="str">
+        <v/>
+      </c>
+      <c r="B1033" t="str">
+        <v>2026-09-13 22:50</v>
+      </c>
+      <c r="C1033" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1033" t="str">
+        <v>אפליקציית נהג - תבניות נסיעה, ויצירת בקשת נסיעה מתוך תבנית</v>
+      </c>
+      <c r="E1033" t="str">
+        <v/>
+      </c>
+      <c r="F1033" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="str">
+        <v/>
+      </c>
+      <c r="B1034" t="str">
+        <v>2026-09-13 22:50</v>
+      </c>
+      <c r="C1034" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1034" t="str">
+        <v>אפליקציית נהג - שכפול בקשת נסיעה</v>
+      </c>
+      <c r="E1034" t="str">
+        <v/>
+      </c>
+      <c r="F1034" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="str">
+        <v/>
+      </c>
+      <c r="B1035" t="str">
+        <v>2026-09-13 22:50</v>
+      </c>
+      <c r="C1035" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1035" t="str">
+        <v>אפליקציית נהג - תצוגת בקשות ונסיעות בשורה מצומצמת יותר (פחות גובה)</v>
+      </c>
+      <c r="E1035" t="str">
+        <v/>
+      </c>
+      <c r="F1035" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="str">
+        <v/>
+      </c>
+      <c r="B1036" t="str">
+        <v>2026-09-13 23:03</v>
+      </c>
+      <c r="C1036" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1036" t="str">
+        <v>אפליקציית הנהג: Google Maps לא נפתח במסך הנסיעה החי</v>
+      </c>
+      <c r="E1036" t="str">
+        <v/>
+      </c>
+      <c r="F1036" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="str">
+        <v/>
+      </c>
+      <c r="B1037" t="str">
+        <v>2026-09-13 23:03</v>
+      </c>
+      <c r="C1037" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1037" t="str">
+        <v>אפליקציית הנהג: הנתיב והאלמנטים הרלוונטיים לא מוצגים על מפת הנסיעה</v>
+      </c>
+      <c r="E1037" t="str">
+        <v/>
+      </c>
+      <c r="F1037" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="str">
+        <v/>
+      </c>
+      <c r="B1038" t="str">
+        <v>2026-09-13 23:48</v>
+      </c>
+      <c r="C1038" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1038" t="str">
+        <v>אפליקציית הנהג: מפת Google עדיין לא עולה במסך הנסיעה החי</v>
+      </c>
+      <c r="E1038" t="str">
+        <v/>
+      </c>
+      <c r="F1038" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="str">
+        <v/>
+      </c>
+      <c r="B1039" t="str">
+        <v>2026-09-13 23:48</v>
+      </c>
+      <c r="C1039" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1039" t="str">
+        <v>עדכון שעת יציאה מהנהג בפעם השנייה - הנסיעה לא מופיעה בלוח הנסיעות כממתינה לאישור</v>
+      </c>
+      <c r="E1039" t="str">
+        <v/>
+      </c>
+      <c r="F1039" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="str">
+        <v/>
+      </c>
+      <c r="B1040" t="str">
+        <v>2026-09-13 23:48</v>
+      </c>
+      <c r="C1040" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1040" t="str">
+        <v>ניהול נסיעות: להציג כמה חלופות נתיב לנסיעה - כרגע מוצגת רק אחת</v>
+      </c>
+      <c r="E1040" t="str">
+        <v/>
+      </c>
+      <c r="F1040" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="str">
+        <v/>
+      </c>
+      <c r="B1041" t="str">
+        <v>2026-09-14 07:30</v>
+      </c>
+      <c r="C1041" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1041" t="str">
+        <v>אפליקציית הנהג: להגדיל את סמלי האלמנטים במפה ולשים אותם על רקע בהיר שמדגיש</v>
+      </c>
+      <c r="E1041" t="str">
+        <v/>
+      </c>
+      <c r="F1041" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="str">
+        <v/>
+      </c>
+      <c r="B1042" t="str">
+        <v>2026-09-14 07:35</v>
+      </c>
+      <c r="C1042" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1042" t="str">
+        <v>אפליקציית DRIVER: מפת שדה התעופה בנסיעה חיה על כל המסך, עם מעקב שממרכז את הרכב וזום להגדלה/הקטנה</v>
+      </c>
+      <c r="E1042" t="str">
+        <v/>
+      </c>
+      <c r="F1042" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="str">
+        <v/>
+      </c>
+      <c r="B1043" t="str">
+        <v>2026-09-14 07:35</v>
+      </c>
+      <c r="C1043" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1043" t="str">
+        <v>אפליקציית DRIVER: לא לאפשר להפעיל שתי נסיעות בו-זמנית</v>
+      </c>
+      <c r="E1043" t="str">
+        <v/>
+      </c>
+      <c r="F1043" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="str">
+        <v/>
+      </c>
+      <c r="B1044" t="str">
+        <v>2026-09-14 08:09</v>
+      </c>
+      <c r="C1044" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1044" t="str">
+        <v>אלמנטים בבסיס: שדה "למי רלוונטי" לכל אלמנט - רכבים / מטוסים (בחירה מרובה)</v>
+      </c>
+      <c r="E1044" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1044" t="str">
+        <v>ac47ec1 (v1.0.208)</v>
+      </c>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="str">
+        <v/>
+      </c>
+      <c r="B1045" t="str">
+        <v>2026-09-14 08:09</v>
+      </c>
+      <c r="C1045" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1045" t="str">
+        <v>אפליקציית נהג: להציג רק אלמנטים שרלוונטיים לרכבים</v>
+      </c>
+      <c r="E1045" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1045" t="str">
+        <v>ac47ec1 (v1.0.208)</v>
+      </c>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="str">
+        <v/>
+      </c>
+      <c r="B1046" t="str">
+        <v>2026-09-14 08:09</v>
+      </c>
+      <c r="C1046" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1046" t="str">
+        <v>חישוב נתיב לרכב הסעה: להתייחס רק לאלמנטים שרלוונטיים לרכבים (עצירה וכו')</v>
+      </c>
+      <c r="E1046" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1046" t="str">
+        <v>ac47ec1 (v1.0.208)</v>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="str">
+        <v/>
+      </c>
+      <c r="B1047" t="str">
+        <v>2026-09-14 08:09</v>
+      </c>
+      <c r="C1047" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1047" t="str">
+        <v>אפליקציית נהג: חצי כיוון נסיעה לאורך קו הנתיב, וכל לג (בין תחנות) בצבע אחר</v>
+      </c>
+      <c r="E1047" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1047" t="str">
+        <v>ac47ec1 (v1.0.208)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1031"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1047"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1047"/>
+  <dimension ref="A1:F1072"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -21347,9 +21347,509 @@
         <v>ac47ec1 (v1.0.208)</v>
       </c>
     </row>
+    <row r="1048">
+      <c r="A1048" t="str">
+        <v/>
+      </c>
+      <c r="B1048" t="str">
+        <v>2026-09-14 08:52</v>
+      </c>
+      <c r="C1048" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1048" t="str">
+        <v>ניהול נהגים: חובה לבחור נהג מרשימה - הרשימה היא הנהגים המורשים במיראז' לבסיס של העמדה</v>
+      </c>
+      <c r="E1048" t="str">
+        <v/>
+      </c>
+      <c r="F1048" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="str">
+        <v/>
+      </c>
+      <c r="B1049" t="str">
+        <v>2026-09-14 08:55</v>
+      </c>
+      <c r="C1049" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1049" t="str">
+        <v>הגדרות עמדה - דגל "עומס רלוונטי לעמדה?": כבוי מסתיר את הזנת נתוני העומס בהגדרות וגם את העומס בעמדה</v>
+      </c>
+      <c r="E1049" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1049" t="str">
+        <v>v1.0.210 · 156f8a5</v>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="str">
+        <v/>
+      </c>
+      <c r="B1050" t="str">
+        <v>2026-09-14 08:55</v>
+      </c>
+      <c r="C1050" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1050" t="str">
+        <v>ניהול עמדות - ברירת מחדל: כל העמדות מכווצות לפי בסיסים</v>
+      </c>
+      <c r="E1050" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1050" t="str">
+        <v>v1.0.210 · 156f8a5</v>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="str">
+        <v/>
+      </c>
+      <c r="B1051" t="str">
+        <v>2026-09-15 09:25</v>
+      </c>
+      <c r="C1051" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1051" t="str">
+        <v>ניהול נסיעות: טאב "בביצוע" לצד קרובות והיסטוריה</v>
+      </c>
+      <c r="E1051" t="str">
+        <v/>
+      </c>
+      <c r="F1051" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="str">
+        <v/>
+      </c>
+      <c r="B1052" t="str">
+        <v>2026-09-15 09:25</v>
+      </c>
+      <c r="C1052" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1052" t="str">
+        <v>ניהול נסיעות: "פתח במפה צפה" לנסיעה בביצוע - Google או מפת הבסיס לבחירה, עם המיקום שהאפליקציה משדרת כל 5 שניות</v>
+      </c>
+      <c r="E1052" t="str">
+        <v/>
+      </c>
+      <c r="F1052" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="str">
+        <v/>
+      </c>
+      <c r="B1053" t="str">
+        <v>2026-09-15 09:25</v>
+      </c>
+      <c r="C1053" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1053" t="str">
+        <v>ניהול נסיעות: "הוסף למפה פתוחה" - כמה נסיעות בביצוע באותה מפה צפה, כל אחת באייקון בצבע אחר</v>
+      </c>
+      <c r="E1053" t="str">
+        <v/>
+      </c>
+      <c r="F1053" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="str">
+        <v/>
+      </c>
+      <c r="B1054" t="str">
+        <v>2026-09-15 09:25</v>
+      </c>
+      <c r="C1054" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1054" t="str">
+        <v>ניהול נסיעות: "הראה היסטוריה" במפה הצפה - שובל נקודות של הקליטות האחרונות בצבע הנסיעה</v>
+      </c>
+      <c r="E1054" t="str">
+        <v/>
+      </c>
+      <c r="F1054" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="str">
+        <v/>
+      </c>
+      <c r="B1055" t="str">
+        <v>2026-09-15 11:00</v>
+      </c>
+      <c r="C1055" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1055" t="str">
+        <v>ניהול נסיעות: כפתורי "פתח במפה צפה" / "הוסף למפה פתוחה" לא מוצגים בנסיעה בביצוע (טבלת הנסיעות המוטמעת בדסק משימה)</v>
+      </c>
+      <c r="E1055" t="str">
+        <v/>
+      </c>
+      <c r="F1055" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="str">
+        <v/>
+      </c>
+      <c r="B1056" t="str">
+        <v>2026-09-15 11:16</v>
+      </c>
+      <c r="C1056" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1056" t="str">
+        <v>ניהול נסיעות (עמדה): כפתורי המפה הצפה עדיין לא מוצגים בנסיעה בביצוע אחרי תיקון ההטמעה</v>
+      </c>
+      <c r="E1056" t="str">
+        <v/>
+      </c>
+      <c r="F1056" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="str">
+        <v/>
+      </c>
+      <c r="B1057" t="str">
+        <v>2026-09-15 11:29</v>
+      </c>
+      <c r="C1057" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1057" t="str">
+        <v>ATSIM: תרחיש או"ק בננה - 10 רביעיות ברצף, הצטרפות בשמשון בגובה 10, הנמכה להקפה 33 בהפרש חצי מייל, נחיתה</v>
+      </c>
+      <c r="E1057" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1057" t="str">
+        <v>atsim abe6c49 - תרחיש sc-5 (עצור), הקפה 33L, delaySec לגלים</v>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="str">
+        <v/>
+      </c>
+      <c r="B1058" t="str">
+        <v>2026-09-15 11:30</v>
+      </c>
+      <c r="C1058" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1058" t="str">
+        <v>תלת מימד/מוד הקפה בשדה אווירי: רכיב אווירי עם גובה מוצג נמוך מגובהו האמיתי ביחס לנקודות (כמו שמשון)</v>
+      </c>
+      <c r="E1058" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1058" t="str">
+        <v>ca4873d v1.0.214 - זווית פתיחה 10° (הכרעת הפקח), תוויות צלע מוזחות במסך</v>
+      </c>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="str">
+        <v/>
+      </c>
+      <c r="B1059" t="str">
+        <v>2026-09-15 11:51</v>
+      </c>
+      <c r="C1059" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1059" t="str">
+        <v>נקודת הצטרפות: לפני קבלת פ"מ לבחור גבהים לכל מספר במבנה (גובה אחד = כל המבנה; עד מספר המטוסים). גבהים תפוסים בכתום + התראה, עדיין ניתן לבחור</v>
+      </c>
+      <c r="E1059" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1059" t="str">
+        <v>b7cae67 (v1.0.215)</v>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="str">
+        <v/>
+      </c>
+      <c r="B1060" t="str">
+        <v>2026-09-15 11:51</v>
+      </c>
+      <c r="C1060" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1060" t="str">
+        <v>נקודת הצטרפות: אחרי קבלה - סידור מספרי המבנה לפי הגבהים שנבחרו (כל מספר בבלוק הגובה שלו)</v>
+      </c>
+      <c r="E1060" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1060" t="str">
+        <v>b7cae67 (v1.0.215)</v>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="str">
+        <v/>
+      </c>
+      <c r="B1061" t="str">
+        <v>2026-09-15 11:55</v>
+      </c>
+      <c r="C1061" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1061" t="str">
+        <v>נקודת הצטרפות: גרירה בבלוק גבהים לא חלקה. גרירת פ"מ שלם מעבירה את כל המבנה עם כל המטוסים לגובה</v>
+      </c>
+      <c r="E1061" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1061" t="str">
+        <v>v1.0.216 - 323ece0</v>
+      </c>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="str">
+        <v/>
+      </c>
+      <c r="B1062" t="str">
+        <v>2026-09-15 11:55</v>
+      </c>
+      <c r="C1062" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1062" t="str">
+        <v>נקודת הצטרפות: גרירת מטוס בודד מפ"מ מורחב מעבירה רק אותו לגובה (מבנה של מטוס אחד/בודד - כל המבנה)</v>
+      </c>
+      <c r="E1062" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1062" t="str">
+        <v>v1.0.216 - 323ece0</v>
+      </c>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="str">
+        <v/>
+      </c>
+      <c r="B1063" t="str">
+        <v>2026-09-15 11:55</v>
+      </c>
+      <c r="C1063" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1063" t="str">
+        <v>הגדרות נקודת הצטרפות: אופציה להציג את המטוסים פרוסים כברירת מחדל ולא את הפ"מים</v>
+      </c>
+      <c r="E1063" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1063" t="str">
+        <v>v1.0.216 - 323ece0</v>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="str">
+        <v/>
+      </c>
+      <c r="B1064" t="str">
+        <v>2026-09-15 12:01</v>
+      </c>
+      <c r="C1064" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1064" t="str">
+        <v>ATSIM תרחיש או"ק בננה: להקרים את התרחיש לתל נוף (התחלה קרובה יותר לשדה)</v>
+      </c>
+      <c r="E1064" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1064" t="str">
+        <v>sc-5 עודכן והורץ מחדש: התחלה 3 מייל לפני שמשון (~5 מייל מתל נוף), מרווח 1.5 מייל</v>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="str">
+        <v/>
+      </c>
+      <c r="B1065" t="str">
+        <v>2026-09-15 12:01</v>
+      </c>
+      <c r="C1065" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1065" t="str">
+        <v>ATSIM תרחיש או"ק בננה: מרווח של מייל וחצי בין כל מטוס במבנה (במקום חצי מייל)</v>
+      </c>
+      <c r="E1065" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1065" t="str">
+        <v>sc-5 עודכן והורץ מחדש: התחלה 3 מייל לפני שמשון (~5 מייל מתל נוף), מרווח 1.5 מייל</v>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="str">
+        <v/>
+      </c>
+      <c r="B1066" t="str">
+        <v>2026-09-15 12:08</v>
+      </c>
+      <c r="C1066" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1066" t="str">
+        <v>שיוך תמונ"א לפ"מ באזור ההקפה לפי או"ק + מספר במבנה (מבנה מפורק), כולל תיקון לא הגיוני (בננה11 ברביעייה = בננה 1)</v>
+      </c>
+      <c r="E1066" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1066" t="str">
+        <v>8fc47dd v1.0.217 - מעקב הקפה אוטומטי (PATTERN_AUTOTRACK_SPEC.md)</v>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="str">
+        <v/>
+      </c>
+      <c r="B1067" t="str">
+        <v>2026-09-15 12:08</v>
+      </c>
+      <c r="C1067" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1067" t="str">
+        <v>רכיב אווירי תואם עד 3 מייל מנקודת הצטרפות: הבהוב ירוק לפ"מ בנקודה; מעל 3 מייל אחרי שהתרחק - אפשר להעלים מהנקודה</v>
+      </c>
+      <c r="E1067" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1067" t="str">
+        <v>8fc47dd v1.0.217 - מעקב הקפה אוטומטי (PATTERN_AUTOTRACK_SPEC.md)</v>
+      </c>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="str">
+        <v/>
+      </c>
+      <c r="B1068" t="str">
+        <v>2026-09-15 12:08</v>
+      </c>
+      <c r="C1068" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1068" t="str">
+        <v>שיבוץ אוטומטי בצלע ההקפה לפי מיקום התמונ"א: עם הרוח / בסיס / פיינל (עד חצי מייל מהצלע)</v>
+      </c>
+      <c r="E1068" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1068" t="str">
+        <v>8fc47dd v1.0.217 - מעקב הקפה אוטומטי (PATTERN_AUTOTRACK_SPEC.md)</v>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="str">
+        <v/>
+      </c>
+      <c r="B1069" t="str">
+        <v>2026-09-15 12:08</v>
+      </c>
+      <c r="C1069" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1069" t="str">
+        <v>זיהוי נחיתה: נחת ולא המריא שוב במשך חצי דקה - סימון נחת ודיווח נחת ל-GAPI</v>
+      </c>
+      <c r="E1069" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1069" t="str">
+        <v>8fc47dd v1.0.217 - מעקב הקפה אוטומטי (PATTERN_AUTOTRACK_SPEC.md)</v>
+      </c>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="str">
+        <v/>
+      </c>
+      <c r="B1070" t="str">
+        <v>2026-09-15 12:08</v>
+      </c>
+      <c r="C1070" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1070" t="str">
+        <v>פ"מ בבסיס שלא דיווח גלגלים ירוקים: הבהוב אדום לפ"מ ולרכיב האווירי + התראה מתפרצת</v>
+      </c>
+      <c r="E1070" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1070" t="str">
+        <v>8fc47dd v1.0.217 - מעקב הקפה אוטומטי (PATTERN_AUTOTRACK_SPEC.md)</v>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="str">
+        <v/>
+      </c>
+      <c r="B1071" t="str">
+        <v>2026-09-15 12:08</v>
+      </c>
+      <c r="C1071" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1071" t="str">
+        <v>טבלת מטוסים חדשה "בהקפה" למי שעזב את נקודת ההצטרפות - מקובצת לפי מסלול נחיתה וממוינת לפי גובה</v>
+      </c>
+      <c r="E1071" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1071" t="str">
+        <v>8fc47dd v1.0.217 - מעקב הקפה אוטומטי (PATTERN_AUTOTRACK_SPEC.md)</v>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="str">
+        <v/>
+      </c>
+      <c r="B1072" t="str">
+        <v>2026-09-15 13:13</v>
+      </c>
+      <c r="C1072" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1072" t="str">
+        <v>ATSIM: תרחיש מבנה שלישייה או"ק דרקון באותו פרופיל (שמשון בגובה 10 -&gt; הקפה 33L בתל נוף, 1.5 מייל בין מטוסים)</v>
+      </c>
+      <c r="E1072" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1072" t="str">
+        <v>ATSIM sc-6 (עצור) - שלישייה אחת, אותו פרופיל של sc-5</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1047"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1072"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1072"/>
+  <dimension ref="A1:F1076"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -21847,9 +21847,89 @@
         <v>ATSIM sc-6 (עצור) - שלישייה אחת, אותו פרופיל של sc-5</v>
       </c>
     </row>
+    <row r="1073">
+      <c r="A1073" t="str">
+        <v/>
+      </c>
+      <c r="B1073" t="str">
+        <v>2026-09-15 13:25</v>
+      </c>
+      <c r="C1073" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1073" t="str">
+        <v>טבלת "בהקפה": לחיצה על ירוקים לוקחת הרבה זמן עד שמתעדכנת</v>
+      </c>
+      <c r="E1073" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1073" t="str">
+        <v>b16116c v1.0.219</v>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="str">
+        <v/>
+      </c>
+      <c r="B1074" t="str">
+        <v>2026-09-15 13:25</v>
+      </c>
+      <c r="C1074" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1074" t="str">
+        <v>מעקב הקפה: כשהמטוס פונה לבסיס - להעביר מיד לסטטוס בסיס</v>
+      </c>
+      <c r="E1074" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1074" t="str">
+        <v>b16116c v1.0.219</v>
+      </c>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="str">
+        <v/>
+      </c>
+      <c r="B1075" t="str">
+        <v>2026-09-15 13:25</v>
+      </c>
+      <c r="C1075" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1075" t="str">
+        <v>מעקב הקפה: סטייה מותרת מהצלע ומהגובה מוגדרת לכל הקפה בפרמטרי השדה, והחישוב לפיה</v>
+      </c>
+      <c r="E1075" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1075" t="str">
+        <v>b16116c v1.0.219</v>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="str">
+        <v/>
+      </c>
+      <c r="B1076" t="str">
+        <v>2026-09-15 13:47</v>
+      </c>
+      <c r="C1076" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1076" t="str">
+        <v>כלל עבודה: כל ההערות והסיכומים של Claude למשתמש בעברית - נרשם ב-CLAUDE.md</v>
+      </c>
+      <c r="E1076" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1076" t="str">
+        <v>274c33c v1.0.220 - CLAUDE.md §שפת התקשורת עם הצוות</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1072"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1076"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1076"/>
+  <dimension ref="A1:F1077"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -21927,9 +21927,29 @@
         <v>274c33c v1.0.220 - CLAUDE.md §שפת התקשורת עם הצוות</v>
       </c>
     </row>
+    <row r="1077">
+      <c r="A1077" t="str">
+        <v/>
+      </c>
+      <c r="B1077" t="str">
+        <v>2026-09-15 19:37</v>
+      </c>
+      <c r="C1077" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1077" t="str">
+        <v>נקודת הצטרפות: אפשר לגרור את טבלת הנקודה (החלון הצף) לקונטיינר החלונות</v>
+      </c>
+      <c r="E1077" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1077" t="str">
+        <v>feat(joining): עגינת טבלת נקודת הצטרפות בקונטיינר</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1076"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1077"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1077"/>
+  <dimension ref="A1:F1100"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -21932,24 +21932,484 @@
         <v/>
       </c>
       <c r="B1077" t="str">
+        <v>2026-09-15 16:08</v>
+      </c>
+      <c r="C1077" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1077" t="str">
+        <v>סטייה מותרת מהגובה בהקפה: נפרד מעל ומתחת. ברירת מחדל כשלא רשום - 500 מתחת, 1500 מעל</v>
+      </c>
+      <c r="E1077" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1077" t="str">
+        <v>fd94d82 v1.0.222</v>
+      </c>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="str">
+        <v/>
+      </c>
+      <c r="B1078" t="str">
+        <v>2026-09-15 16:22</v>
+      </c>
+      <c r="C1078" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1078" t="str">
+        <v>הגדרת עמדה: לוגיקות והתראות של תמונ"א פועלות גם כשהתמונ"א אינה מוצגת (ברירת מחדל - כן)</v>
+      </c>
+      <c r="E1078" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1078" t="str">
+        <v>1c6d381 v1.0.223</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="str">
+        <v/>
+      </c>
+      <c r="B1079" t="str">
+        <v>2026-09-15 16:22</v>
+      </c>
+      <c r="C1079" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1079" t="str">
+        <v>בעמדה, בהגדרות: מתג ללוגיקות תמונ"א כשהיא לא מוצגת, ומתג ללוגיקות תמונ"א כשהיא מוצגת</v>
+      </c>
+      <c r="E1079" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1079" t="str">
+        <v>1c6d381 v1.0.223</v>
+      </c>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="str">
+        <v/>
+      </c>
+      <c r="B1080" t="str">
+        <v>2026-09-15 16:55</v>
+      </c>
+      <c r="C1080" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1080" t="str">
+        <v>מעקב הקפה: דרקון 3 בפיינל לא סומן נחת אחרי יותר מ-30 שניות על הקרקע (בטבלת בהקפה - לא משודך לרכיב אווירי)</v>
+      </c>
+      <c r="E1080" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1080" t="str">
+        <v>6e43c93 v1.0.224</v>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="str">
+        <v/>
+      </c>
+      <c r="B1081" t="str">
+        <v>2026-09-15 17:01</v>
+      </c>
+      <c r="C1081" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1081" t="str">
+        <v>מתגי "לוגיקות כשמוצגת / כשלא מוצגת" - להעביר מפאנל התמונ"א להגדרות העמדה, עם כיתוב שהם רלוונטיים לתמונ"א</v>
+      </c>
+      <c r="E1081" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1081" t="str">
+        <v>6e43c93 v1.0.224</v>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="str">
+        <v/>
+      </c>
+      <c r="B1082" t="str">
+        <v>2026-09-15 17:16</v>
+      </c>
+      <c r="C1082" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1082" t="str">
+        <v>נקודת הצטרפות: אחרי "קבל" וחלוקת גבהים לפ"מ - לוקח הרבה זמן עד שמתחלק לבלוקים, נעלם וחוזר (הבהוב)</v>
+      </c>
+      <c r="E1082" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1082" t="str">
+        <v>0eba4fe (v1.0.226)</v>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="str">
+        <v/>
+      </c>
+      <c r="B1083" t="str">
+        <v>2026-09-15 17:16</v>
+      </c>
+      <c r="C1083" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1083" t="str">
+        <v>נקודת הצטרפות: אופציה בב"מ להציג רק מטוסים ללא פ"מ (כאילו תמיד פרוס) - המשתמש לא מוצא את ההגדרה</v>
+      </c>
+      <c r="E1083" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1083" t="str">
+        <v>0eba4fe (v1.0.226)</v>
+      </c>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="str">
+        <v/>
+      </c>
+      <c r="B1084" t="str">
+        <v>2026-09-15 17:48</v>
+      </c>
+      <c r="C1084" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1084" t="str">
+        <v>בעמדת שדה תעופה, הקטנת חלון הפ"מים מצמצמת את הפ"מים למלבנים ריקים - צריך להתנהג כמו בשאר העמדות</v>
+      </c>
+      <c r="E1084" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1084" t="str">
+        <v>קומיט 8355581 (v1.0.225)</v>
+      </c>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="str">
+        <v/>
+      </c>
+      <c r="B1085" t="str">
+        <v>2026-09-15 18:18</v>
+      </c>
+      <c r="C1085" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1085" t="str">
+        <v>ATSIM: תרחיש או"ק יהלום רביעייה ואחריו או"ק ירח שלישייה, באותו פרופיל (שמשון -&gt; הקפה 33L תל נוף, 1.5 מייל)</v>
+      </c>
+      <c r="E1085" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1085" t="str">
+        <v>ATSIM sc-7 רץ; atsim 1979e53 - מבנים בגדלים שונים ברצף</v>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="str">
+        <v/>
+      </c>
+      <c r="B1086" t="str">
+        <v>2026-09-15 18:24</v>
+      </c>
+      <c r="C1086" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1086" t="str">
+        <v>מטוס שיוצא מנקודת הצטרפות (עבר לעה"ר וכו') - פתיחה אוטומטית של החלון הצף "הקפה"</v>
+      </c>
+      <c r="E1086" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1086" t="str">
+        <v>1717599 (v1.0.227)</v>
+      </c>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="str">
+        <v/>
+      </c>
+      <c r="B1087" t="str">
         <v>2026-09-15 19:37</v>
       </c>
-      <c r="C1077" t="str">
-        <v>שיפור לתכולה קיימת</v>
-      </c>
-      <c r="D1077" t="str">
+      <c r="C1087" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1087" t="str">
         <v>נקודת הצטרפות: אפשר לגרור את טבלת הנקודה (החלון הצף) לקונטיינר החלונות</v>
       </c>
-      <c r="E1077" t="str">
-        <v>כן</v>
-      </c>
-      <c r="F1077" t="str">
+      <c r="E1087" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1087" t="str">
         <v>feat(joining): עגינת טבלת נקודת הצטרפות בקונטיינר</v>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="str">
+        <v/>
+      </c>
+      <c r="B1088" t="str">
+        <v>2026-09-15 19:43</v>
+      </c>
+      <c r="C1088" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1088" t="str">
+        <v>נקודת הצטרפות בעמדה: חלון מאפיינים בפאנל הנקודה לעדכון הגדרת "מטוסים בלבד" ישירות מהעמדה</v>
+      </c>
+      <c r="E1088" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1088" t="str">
+        <v>fa339a6 (v1.0.232)</v>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="str">
+        <v/>
+      </c>
+      <c r="B1089" t="str">
+        <v>2026-09-15 19:46</v>
+      </c>
+      <c r="C1089" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1089" t="str">
+        <v>נקודת הצטרפות: פקד בשורת המטוס עולה על כפתור הירוקים</v>
+      </c>
+      <c r="E1089" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1089" t="str">
+        <v>v1.0.229 - a12eaf6</v>
+      </c>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="str">
+        <v/>
+      </c>
+      <c r="B1090" t="str">
+        <v>2026-09-15 19:46</v>
+      </c>
+      <c r="C1090" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1090" t="str">
+        <v>נקודת הצטרפות: קו מפריד ברור יותר בין בלוקי הגבהים</v>
+      </c>
+      <c r="E1090" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1090" t="str">
+        <v>v1.0.229 - a12eaf6</v>
+      </c>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="str">
+        <v/>
+      </c>
+      <c r="B1091" t="str">
+        <v>2026-09-15 19:46</v>
+      </c>
+      <c r="C1091" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1091" t="str">
+        <v>נקודת הצטרפות: ביטול "שים בהקפה"/"הוצא מההקפה" - עה"ר בתפריט = בהקפה; להוסיף לתפריט "בנקודת הצטרפות" כברירת מחדל</v>
+      </c>
+      <c r="E1091" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1091" t="str">
+        <v>v1.0.229 - a12eaf6</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="str">
+        <v/>
+      </c>
+      <c r="B1092" t="str">
+        <v>2026-09-15 20:00</v>
+      </c>
+      <c r="C1092" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1092" t="str">
+        <v>ניהול שדה תעופה: בנקודה מסוג דת"ק - קביעת סדר עדיפות לנחיתה (רשימת מספרי מסלולים בסדר רץ)</v>
+      </c>
+      <c r="E1092" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1092" t="str">
+        <v>commit 1990082 (v1.0.230)</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="str">
+        <v/>
+      </c>
+      <c r="B1093" t="str">
+        <v>2026-09-15 20:00</v>
+      </c>
+      <c r="C1093" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1093" t="str">
+        <v>נקודת הצטרפות: מבנה שמגיע מחולק אוטומטית למסלולים לפי סדר העדיפויות, רק מסלולים פתוחים לנחיתה</v>
+      </c>
+      <c r="E1093" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1093" t="str">
+        <v>commit 1990082 (v1.0.230)</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="str">
+        <v/>
+      </c>
+      <c r="B1094" t="str">
+        <v>2026-09-15 20:14</v>
+      </c>
+      <c r="C1094" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1094" t="str">
+        <v>קונפליקט בהקפה: רכיב אווירי אחר שנכנס לטווח ההקפה (סטייה מהצלע ומהגובה לפי פרמטרי השדה) כשיש בה מטוס - התראה מתפרצת והבהוב למי שבקונפליקט</v>
+      </c>
+      <c r="E1094" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1094" t="str">
+        <v>835c86c v1.0.231 - PATTERN_AUTOTRACK_SPEC §10</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="str">
+        <v/>
+      </c>
+      <c r="B1095" t="str">
+        <v>2026-09-15 20:23</v>
+      </c>
+      <c r="C1095" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1095" t="str">
+        <v>FLOW של פ"מ בקליק: טבלה כרונולוגית של מסלול המטוס - דת"ק, הסעה, המראה, נקודות העברה, עמדות שקיבלו בפועל, בת"ק</v>
+      </c>
+      <c r="E1095" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1095" t="str">
+        <v>dc37138 - v1.0.234</v>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="str">
+        <v/>
+      </c>
+      <c r="B1096" t="str">
+        <v>2026-09-15 20:23</v>
+      </c>
+      <c r="C1096" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1096" t="str">
+        <v>FLOW מרוכז בשאילתא: תצוגה טבלאית של ה-FLOW והמיקום הנוכחי של כל הפ"מים, זמין בכל עמדה</v>
+      </c>
+      <c r="E1096" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1096" t="str">
+        <v>dc37138 - v1.0.234</v>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="str">
+        <v/>
+      </c>
+      <c r="B1097" t="str">
+        <v>2026-09-15 21:00</v>
+      </c>
+      <c r="C1097" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1097" t="str">
+        <v>נקודת הצטרפות, שורת מטוס: בתפריט המצב "בנקודת הצטרפות" -&gt; "הצטרפות" (להקטנת השדה)</v>
+      </c>
+      <c r="E1097" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1097" t="str">
+        <v>b5dfd6e (v1.0.233)</v>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="str">
+        <v/>
+      </c>
+      <c r="B1098" t="str">
+        <v>2026-09-15 21:00</v>
+      </c>
+      <c r="C1098" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1098" t="str">
+        <v>נקודת הצטרפות, שורת מטוס: בבורר המסלול "בחר מסלול" -&gt; "מסלול"</v>
+      </c>
+      <c r="E1098" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1098" t="str">
+        <v>b5dfd6e (v1.0.233)</v>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="str">
+        <v/>
+      </c>
+      <c r="B1099" t="str">
+        <v>2026-09-15 21:03</v>
+      </c>
+      <c r="C1099" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1099" t="str">
+        <v>נקודת הצטרפות: פעולה "סדר מחדש מסלולים לפי דת"קים" - חלוקה מחדש של מסלולי הנחיתה לפי סדר העדיפויות</v>
+      </c>
+      <c r="E1099" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1099" t="str">
+        <v>commit 5df8880 (v1.0.235)</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="str">
+        <v/>
+      </c>
+      <c r="B1100" t="str">
+        <v>2026-09-15 21:03</v>
+      </c>
+      <c r="C1100" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1100" t="str">
+        <v>נקודת הצטרפות: הדגשת מסלול שנקבע בחלוקה אוטומטית, וסימון שמסלול נבחר ידנית</v>
+      </c>
+      <c r="E1100" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1100" t="str">
+        <v>commit 5df8880 (v1.0.235)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1077"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1100"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1100"/>
+  <dimension ref="A1:F1101"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22407,9 +22407,29 @@
         <v>commit 5df8880 (v1.0.235)</v>
       </c>
     </row>
+    <row r="1101">
+      <c r="A1101" t="str">
+        <v/>
+      </c>
+      <c r="B1101" t="str">
+        <v>2026-09-15 21:26</v>
+      </c>
+      <c r="C1101" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1101" t="str">
+        <v>חלון נקודת הצטרפות וחלון בהקפה - בהעברה לקונטיינר החלונות כיוון ימין-שמאל מתהפך (נכתב הפוך)</v>
+      </c>
+      <c r="E1101" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1101" t="str">
+        <v>REFACTOR_LOG #050 - גוף משבצת הקונטיינר מחזיר direction לפי השפה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1100"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1101"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1101"/>
+  <dimension ref="A1:F1104"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22427,9 +22427,69 @@
         <v>REFACTOR_LOG #050 - גוף משבצת הקונטיינר מחזיר direction לפי השפה</v>
       </c>
     </row>
+    <row r="1102">
+      <c r="A1102" t="str">
+        <v/>
+      </c>
+      <c r="B1102" t="str">
+        <v>2026-09-15 21:37</v>
+      </c>
+      <c r="C1102" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1102" t="str">
+        <v>נקודת הצטרפות: בלי אייקון/תווית למסלול - רק צביעת בורר המסלול לפי ידני או אוטומטי</v>
+      </c>
+      <c r="E1102" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1102" t="str">
+        <v>v1.0.238 - דת"קים משותפים לבסיס האב + צבע בלבד</v>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="str">
+        <v/>
+      </c>
+      <c r="B1103" t="str">
+        <v>2026-09-15 21:37</v>
+      </c>
+      <c r="C1103" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1103" t="str">
+        <v>נקודת הצטרפות בחא 8: המבנה לא מחולק למסלולים לפי סדר העדיפויות של הדת"ק</v>
+      </c>
+      <c r="E1103" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1103" t="str">
+        <v>v1.0.238 - דת"קים משותפים לבסיס האב + צבע בלבד</v>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="str">
+        <v/>
+      </c>
+      <c r="B1104" t="str">
+        <v>2026-09-15 21:37</v>
+      </c>
+      <c r="C1104" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1104" t="str">
+        <v>סדר עדיפויות לנחיתה לדת"ק משותף לכל השדות תחת אותו בסיס אב - הגדרה במקום אחד מסונכרנת לכולם</v>
+      </c>
+      <c r="E1104" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1104" t="str">
+        <v>v1.0.238 - דת"קים משותפים לבסיס האב + צבע בלבד</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1104"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1104"/>
+  <dimension ref="A1:F1106"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22487,9 +22487,49 @@
         <v>v1.0.238 - דת"קים משותפים לבסיס האב + צבע בלבד</v>
       </c>
     </row>
+    <row r="1105">
+      <c r="A1105" t="str">
+        <v/>
+      </c>
+      <c r="B1105" t="str">
+        <v>2026-09-16 19:30</v>
+      </c>
+      <c r="C1105" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1105" t="str">
+        <v>מערכת הקלטת פעולות במסך - הקלטת כל התצוגה של העמדה לקובץ וידאו</v>
+      </c>
+      <c r="E1105" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1105" t="str">
+        <v>3080e23 - feat(screen-rec)</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="str">
+        <v/>
+      </c>
+      <c r="B1106" t="str">
+        <v>2026-09-16 19:30</v>
+      </c>
+      <c r="C1106" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1106" t="str">
+        <v>ניהול טכני: הגדרת PATH לשמירת קובץ ההקלטה, פר בסיס</v>
+      </c>
+      <c r="E1106" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1106" t="str">
+        <v>3080e23 - feat(screen-rec)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1104"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1106"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1106"/>
+  <dimension ref="A1:F1107"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22527,9 +22527,29 @@
         <v>3080e23 - feat(screen-rec)</v>
       </c>
     </row>
+    <row r="1107">
+      <c r="A1107" t="str">
+        <v/>
+      </c>
+      <c r="B1107" t="str">
+        <v>2026-09-16 20:31</v>
+      </c>
+      <c r="C1107" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1107" t="str">
+        <v>הקלטת מסך גם מהדפדפן - העמדה שולחת את הווידאו בנתחים לשרת, והשרת כותב ל-PATH</v>
+      </c>
+      <c r="E1107" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1107" t="str">
+        <v>21d4fa3 - feat(screen-rec)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1106"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1107"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1107"/>
+  <dimension ref="A1:F1108"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22547,9 +22547,29 @@
         <v>21d4fa3 - feat(screen-rec)</v>
       </c>
     </row>
+    <row r="1108">
+      <c r="A1108" t="str">
+        <v/>
+      </c>
+      <c r="B1108" t="str">
+        <v>2026-09-16 22:04</v>
+      </c>
+      <c r="C1108" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1108" t="str">
+        <v>הקלטת מסך באלקטרון: "נתיב השמירה אינו נגיש מהעמדה" - ההקלטה לא מתחילה</v>
+      </c>
+      <c r="E1108" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1108" t="str">
+        <v>1c780c7 - הנתיב שהוגדר היה C: (שורש כונן)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1107"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1108"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1108"/>
+  <dimension ref="A1:F1109"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22567,9 +22567,29 @@
         <v>1c780c7 - הנתיב שהוגדר היה C: (שורש כונן)</v>
       </c>
     </row>
+    <row r="1109">
+      <c r="A1109" t="str">
+        <v/>
+      </c>
+      <c r="B1109" t="str">
+        <v>2026-09-16 22:24</v>
+      </c>
+      <c r="C1109" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1109" t="str">
+        <v>הקלטת מסך: ההודעה אומרת "אין הרשאה" גם כשהכונן שבנתיב אינו קיים - ולא אומרת איזה כונן</v>
+      </c>
+      <c r="E1109" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1109" t="str">
+        <v>0199654 - הכונן D: לא קיים במכונה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1108"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1109"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1109"/>
+  <dimension ref="A1:F1110"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22587,9 +22587,29 @@
         <v>0199654 - הכונן D: לא קיים במכונה</v>
       </c>
     </row>
+    <row r="1110">
+      <c r="A1110" t="str">
+        <v/>
+      </c>
+      <c r="B1110" t="str">
+        <v>2026-09-17 11:28</v>
+      </c>
+      <c r="C1110" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1110" t="str">
+        <v>הקלטת מסך: הודעת הכשל נשארת תקועה אחרי שהנתיב תוקן בניהול הטכני, ואין ניסיון חוזר אוטומטי</v>
+      </c>
+      <c r="E1110" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1110" t="str">
+        <v>fbdb855 - ניקוי כשל + התאוששות אוטומטית</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1109"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1110"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1110"/>
+  <dimension ref="A1:F1111"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22607,9 +22607,29 @@
         <v>fbdb855 - ניקוי כשל + התאוששות אוטומטית</v>
       </c>
     </row>
+    <row r="1111">
+      <c r="A1111" t="str">
+        <v/>
+      </c>
+      <c r="B1111" t="str">
+        <v>2026-09-17 12:08</v>
+      </c>
+      <c r="C1111" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1111" t="str">
+        <v>הקלטת מסך: "היעד C: אינו קיים בעמדה הזו" - ההודעה לא מבדילה בין העמדה לשרת, וההקלטה נופלת למסלול השרת</v>
+      </c>
+      <c r="E1111" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1111" t="str">
+        <v>42cec38 - הודעות פר מסלול + server_root_ok</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1110"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1111"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1111"/>
+  <dimension ref="A1:F1112"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22627,9 +22627,29 @@
         <v>42cec38 - הודעות פר מסלול + server_root_ok</v>
       </c>
     </row>
+    <row r="1112">
+      <c r="A1112" t="str">
+        <v/>
+      </c>
+      <c r="B1112" t="str">
+        <v>2026-09-17 12:28</v>
+      </c>
+      <c r="C1112" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1112" t="str">
+        <v>הרצת אפליקציית העמדה נכשלת: Electron failed to install correctly (הבינארי חסר ב-node_modules/electron)</v>
+      </c>
+      <c r="E1112" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1112" t="str">
+        <v>64809e2 - חולץ מהמחסן + תועד ב-DEV_GUIDE</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1111"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1112"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1112"/>
+  <dimension ref="A1:F1113"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22647,9 +22647,29 @@
         <v>64809e2 - חולץ מהמחסן + תועד ב-DEV_GUIDE</v>
       </c>
     </row>
+    <row r="1113">
+      <c r="A1113" t="str">
+        <v/>
+      </c>
+      <c r="B1113" t="str">
+        <v>2026-09-17 22:51</v>
+      </c>
+      <c r="C1113" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1113" t="str">
+        <v>הקלטת מסך לא עובדת באפליקציית העמדה (electron:railway) וגם לא בדפדפן - ובלי שמוצגת סיבה</v>
+      </c>
+      <c r="E1113" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1113" t="str">
+        <v>68b527e - did-start-loading עצר את ההקלטה; WEB דורש שרת שרואה את הנתיב</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1112"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1113"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1113"/>
+  <dimension ref="A1:F1114"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22667,9 +22667,29 @@
         <v>68b527e - did-start-loading עצר את ההקלטה; WEB דורש שרת שרואה את הנתיב</v>
       </c>
     </row>
+    <row r="1114">
+      <c r="A1114" t="str">
+        <v/>
+      </c>
+      <c r="B1114" t="str">
+        <v>2026-09-18 11:22</v>
+      </c>
+      <c r="C1114" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1114" t="str">
+        <v>הקלטת מסך מדפדפן מול שרת מרוחק (Railway) - איך שומרים כשהשרת אינו רואה את הנתיב</v>
+      </c>
+      <c r="E1114" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1114" t="str">
+        <v>5f03f67 - הדפדפן כותב לתיקייה שנבחרת פעם אחת</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1113"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1114"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1114"/>
+  <dimension ref="A1:F1116"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22687,9 +22687,49 @@
         <v>5f03f67 - הדפדפן כותב לתיקייה שנבחרת פעם אחת</v>
       </c>
     </row>
+    <row r="1115">
+      <c r="A1115" t="str">
+        <v/>
+      </c>
+      <c r="B1115" t="str">
+        <v>2026-09-19 14:07</v>
+      </c>
+      <c r="C1115" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1115" t="str">
+        <v>עמדת טבלנית: עמודות מקובעות בצד ימין זזות בגלילה אופקית ולפעמים נכנסות מתחת לחלון הפ"מים</v>
+      </c>
+      <c r="E1115" t="str">
+        <v/>
+      </c>
+      <c r="F1115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="str">
+        <v/>
+      </c>
+      <c r="B1116" t="str">
+        <v>2026-09-19 14:07</v>
+      </c>
+      <c r="C1116" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1116" t="str">
+        <v>עמדת טבלנית: בגלילה אנכית השורות עולות על שורת הכותרות</v>
+      </c>
+      <c r="E1116" t="str">
+        <v/>
+      </c>
+      <c r="F1116" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1114"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1116"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -22701,10 +22701,10 @@
         <v>עמדת טבלנית: עמודות מקובעות בצד ימין זזות בגלילה אופקית ולפעמים נכנסות מתחת לחלון הפ"מים</v>
       </c>
       <c r="E1115" t="str">
-        <v/>
+        <v>כן</v>
       </c>
       <c r="F1115" t="str">
-        <v/>
+        <v>bde514e - מדידה חיה + רקע לכותרות</v>
       </c>
     </row>
     <row r="1116">
@@ -22721,10 +22721,10 @@
         <v>עמדת טבלנית: בגלילה אנכית השורות עולות על שורת הכותרות</v>
       </c>
       <c r="E1116" t="str">
-        <v/>
+        <v>כן</v>
       </c>
       <c r="F1116" t="str">
-        <v/>
+        <v>bde514e - מדידה חיה + רקע לכותרות</v>
       </c>
     </row>
   </sheetData>

--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1116"/>
+  <dimension ref="A1:F1117"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22727,9 +22727,29 @@
         <v>bde514e - מדידה חיה + רקע לכותרות</v>
       </c>
     </row>
+    <row r="1117">
+      <c r="A1117" t="str">
+        <v/>
+      </c>
+      <c r="B1117" t="str">
+        <v>2026-09-19 14:35</v>
+      </c>
+      <c r="C1117" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1117" t="str">
+        <v>ניהול מפות: בהעלאת מפה חדשה לאפשר הדבקה (Ctrl+V) של תמונה שנגזרה/צולמה מהלוח במקום בחירת קובץ</v>
+      </c>
+      <c r="E1117" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1117" t="str">
+        <v>feature/map-upload-paste - Ctrl+V + כפתור הדבק + תצוגה מקדימה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1116"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1117"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1117"/>
+  <dimension ref="A1:F1118"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22747,9 +22747,29 @@
         <v>feature/map-upload-paste - Ctrl+V + כפתור הדבק + תצוגה מקדימה</v>
       </c>
     </row>
+    <row r="1118">
+      <c r="A1118" t="str">
+        <v/>
+      </c>
+      <c r="B1118" t="str">
+        <v>2026-09-19 14:53</v>
+      </c>
+      <c r="C1118" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1118" t="str">
+        <v>עיגון מפה: הדבקת נ"צ עשרוני בפורמט Google Earth (31.819509, 34.796090) והמרה אוטומטית לפורמט חה"א (N/E מעלות-דקות-שניות)</v>
+      </c>
+      <c r="E1118" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1118" t="str">
+        <v>useAnchorCoordPaste - Ctrl+V/כפתור, עשרוני+DMS+DDM, בניהול שדות ובעורך האזורים</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1117"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1118"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,15 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1118"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="72.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="40.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:F1119"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -22767,9 +22759,29 @@
         <v>useAnchorCoordPaste - Ctrl+V/כפתור, עשרוני+DMS+DDM, בניהול שדות ובעורך האזורים</v>
       </c>
     </row>
+    <row r="1119">
+      <c r="A1119" t="str">
+        <v/>
+      </c>
+      <c r="B1119" t="str">
+        <v>2026-09-19 16:40</v>
+      </c>
+      <c r="C1119" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1119" t="str">
+        <v>דסק חופשי: רקע שורות (גובה שורה מתכוונן) או משבצות (גודל מתכוונן), קו מקווקו / מנוקד / רציף</v>
+      </c>
+      <c r="E1119" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1119" t="str">
+        <v>src/utils/deskBackground.ts + כפתור ▦ בכותרת הדסק</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1118"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1119"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1119"/>
+  <dimension ref="A1:F1121"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="72.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="40.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -22779,9 +22787,49 @@
         <v>src/utils/deskBackground.ts + כפתור ▦ בכותרת הדסק</v>
       </c>
     </row>
+    <row r="1120">
+      <c r="A1120" t="str">
+        <v/>
+      </c>
+      <c r="B1120" t="str">
+        <v>2026-09-19 16:44</v>
+      </c>
+      <c r="C1120" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1120" t="str">
+        <v>כלי ציור על מפה: פוליגון סגור - דקירת נקודות שמתחברות בקו, והאחרונה נסגרת לראשונה</v>
+      </c>
+      <c r="E1120" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1120" t="str">
+        <v>REFACTOR_LOG #052</v>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="str">
+        <v/>
+      </c>
+      <c r="B1121" t="str">
+        <v>2026-09-19 16:44</v>
+      </c>
+      <c r="C1121" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1121" t="str">
+        <v>כלי ציור על מפה: פוליגון פתוח - דקירת נקודות שמתחברות בקו, בלי סגירה לראשונה</v>
+      </c>
+      <c r="E1121" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1121" t="str">
+        <v>REFACTOR_LOG #052</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1119"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1121"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1121"/>
+  <dimension ref="A1:F1124"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22827,9 +22827,69 @@
         <v>REFACTOR_LOG #052</v>
       </c>
     </row>
+    <row r="1122">
+      <c r="A1122" t="str">
+        <v/>
+      </c>
+      <c r="B1122" t="str">
+        <v>2026-09-19 16:54</v>
+      </c>
+      <c r="C1122" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1122" t="str">
+        <v>פ"מ שכבר בנקודת העברה ונגרר לנקודת העברה מעמדה אחרת - טופס תיאום בעמדה הגוררת (מאושר/לא אושר); באישור ההקצאה הקודמת נמחקת</v>
+      </c>
+      <c r="E1122" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1122" t="str">
+        <v>server/routes/transferTakeovers.js + TransferTakeoverDialog</v>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="str">
+        <v/>
+      </c>
+      <c r="B1123" t="str">
+        <v>2026-09-19 16:54</v>
+      </c>
+      <c r="C1123" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1123" t="str">
+        <v>באותו מקרה - התראה עם אישור/דחייה גם בעמדה שהפ"מ כבר אצלה בדרך לנקודת העברה</v>
+      </c>
+      <c r="E1123" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1123" t="str">
+        <v>server/routes/transferTakeovers.js + TransferTakeoverDialog</v>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="str">
+        <v/>
+      </c>
+      <c r="B1124" t="str">
+        <v>2026-09-19 16:54</v>
+      </c>
+      <c r="C1124" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1124" t="str">
+        <v>גרירת פ"מ לעמדה/מפה (לא דרך העברה) כשהוא קיים גם בעמדה אחרת - הודעה "שים לב פ"מ X נמצא גם בעמדה Y"</v>
+      </c>
+      <c r="E1124" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1124" t="str">
+        <v>server/routes/transferTakeovers.js + TransferTakeoverDialog</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1121"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1124"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1124"/>
+  <dimension ref="A1:F1125"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22772,19 +22772,19 @@
         <v/>
       </c>
       <c r="B1119" t="str">
-        <v>2026-09-19 16:40</v>
+        <v>2026-09-19 14:57</v>
       </c>
       <c r="C1119" t="str">
-        <v>תכולה חדשה</v>
+        <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1119" t="str">
-        <v>דסק חופשי: רקע שורות (גובה שורה מתכוונן) או משבצות (גודל מתכוונן), קו מקווקו / מנוקד / רציף</v>
+        <v>אפליקציית נהג - התרעת התקרבות לרמזור סוגר מ-50 מ' ל-100 מ'</v>
       </c>
       <c r="E1119" t="str">
-        <v>כן</v>
+        <v/>
       </c>
       <c r="F1119" t="str">
-        <v>src/utils/deskBackground.ts + כפתור ▦ בכותרת הדסק</v>
+        <v/>
       </c>
     </row>
     <row r="1120">
@@ -22792,19 +22792,19 @@
         <v/>
       </c>
       <c r="B1120" t="str">
-        <v>2026-09-19 16:44</v>
+        <v>2026-09-19 16:40</v>
       </c>
       <c r="C1120" t="str">
         <v>תכולה חדשה</v>
       </c>
       <c r="D1120" t="str">
-        <v>כלי ציור על מפה: פוליגון סגור - דקירת נקודות שמתחברות בקו, והאחרונה נסגרת לראשונה</v>
+        <v>דסק חופשי: רקע שורות (גובה שורה מתכוונן) או משבצות (גודל מתכוונן), קו מקווקו / מנוקד / רציף</v>
       </c>
       <c r="E1120" t="str">
         <v>כן</v>
       </c>
       <c r="F1120" t="str">
-        <v>REFACTOR_LOG #052</v>
+        <v>src/utils/deskBackground.ts + כפתור ▦ בכותרת הדסק</v>
       </c>
     </row>
     <row r="1121">
@@ -22818,7 +22818,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1121" t="str">
-        <v>כלי ציור על מפה: פוליגון פתוח - דקירת נקודות שמתחברות בקו, בלי סגירה לראשונה</v>
+        <v>כלי ציור על מפה: פוליגון סגור - דקירת נקודות שמתחברות בקו, והאחרונה נסגרת לראשונה</v>
       </c>
       <c r="E1121" t="str">
         <v>כן</v>
@@ -22832,19 +22832,19 @@
         <v/>
       </c>
       <c r="B1122" t="str">
-        <v>2026-09-19 16:54</v>
+        <v>2026-09-19 16:44</v>
       </c>
       <c r="C1122" t="str">
         <v>תכולה חדשה</v>
       </c>
       <c r="D1122" t="str">
-        <v>פ"מ שכבר בנקודת העברה ונגרר לנקודת העברה מעמדה אחרת - טופס תיאום בעמדה הגוררת (מאושר/לא אושר); באישור ההקצאה הקודמת נמחקת</v>
+        <v>כלי ציור על מפה: פוליגון פתוח - דקירת נקודות שמתחברות בקו, בלי סגירה לראשונה</v>
       </c>
       <c r="E1122" t="str">
         <v>כן</v>
       </c>
       <c r="F1122" t="str">
-        <v>server/routes/transferTakeovers.js + TransferTakeoverDialog</v>
+        <v>REFACTOR_LOG #052</v>
       </c>
     </row>
     <row r="1123">
@@ -22858,7 +22858,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1123" t="str">
-        <v>באותו מקרה - התראה עם אישור/דחייה גם בעמדה שהפ"מ כבר אצלה בדרך לנקודת העברה</v>
+        <v>פ"מ שכבר בנקודת העברה ונגרר לנקודת העברה מעמדה אחרת - טופס תיאום בעמדה הגוררת (מאושר/לא אושר); באישור ההקצאה הקודמת נמחקת</v>
       </c>
       <c r="E1123" t="str">
         <v>כן</v>
@@ -22878,7 +22878,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1124" t="str">
-        <v>גרירת פ"מ לעמדה/מפה (לא דרך העברה) כשהוא קיים גם בעמדה אחרת - הודעה "שים לב פ"מ X נמצא גם בעמדה Y"</v>
+        <v>באותו מקרה - התראה עם אישור/דחייה גם בעמדה שהפ"מ כבר אצלה בדרך לנקודת העברה</v>
       </c>
       <c r="E1124" t="str">
         <v>כן</v>
@@ -22887,9 +22887,29 @@
         <v>server/routes/transferTakeovers.js + TransferTakeoverDialog</v>
       </c>
     </row>
+    <row r="1125">
+      <c r="A1125" t="str">
+        <v/>
+      </c>
+      <c r="B1125" t="str">
+        <v>2026-09-19 16:54</v>
+      </c>
+      <c r="C1125" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1125" t="str">
+        <v>גרירת פ"מ לעמדה/מפה (לא דרך העברה) כשהוא קיים גם בעמדה אחרת - הודעה "שים לב פ"מ X נמצא גם בעמדה Y"</v>
+      </c>
+      <c r="E1125" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1125" t="str">
+        <v>server/routes/transferTakeovers.js + TransferTakeoverDialog</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1125"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1125"/>
+  <dimension ref="A1:F1126"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22792,19 +22792,19 @@
         <v/>
       </c>
       <c r="B1120" t="str">
-        <v>2026-09-19 16:40</v>
+        <v>2026-09-19 15:11</v>
       </c>
       <c r="C1120" t="str">
-        <v>תכולה חדשה</v>
+        <v>תקלה</v>
       </c>
       <c r="D1120" t="str">
-        <v>דסק חופשי: רקע שורות (גובה שורה מתכוונן) או משבצות (גודל מתכוונן), קו מקווקו / מנוקד / רציף</v>
+        <v>אפליקציית נהג - התקרבות לרמזור ברחוב הדליה לא הקפיצה התרעה כלל</v>
       </c>
       <c r="E1120" t="str">
-        <v>כן</v>
+        <v/>
       </c>
       <c r="F1120" t="str">
-        <v>src/utils/deskBackground.ts + כפתור ▦ בכותרת הדסק</v>
+        <v/>
       </c>
     </row>
     <row r="1121">
@@ -22812,19 +22812,19 @@
         <v/>
       </c>
       <c r="B1121" t="str">
-        <v>2026-09-19 16:44</v>
+        <v>2026-09-19 16:40</v>
       </c>
       <c r="C1121" t="str">
         <v>תכולה חדשה</v>
       </c>
       <c r="D1121" t="str">
-        <v>כלי ציור על מפה: פוליגון סגור - דקירת נקודות שמתחברות בקו, והאחרונה נסגרת לראשונה</v>
+        <v>דסק חופשי: רקע שורות (גובה שורה מתכוונן) או משבצות (גודל מתכוונן), קו מקווקו / מנוקד / רציף</v>
       </c>
       <c r="E1121" t="str">
         <v>כן</v>
       </c>
       <c r="F1121" t="str">
-        <v>REFACTOR_LOG #052</v>
+        <v>src/utils/deskBackground.ts + כפתור ▦ בכותרת הדסק</v>
       </c>
     </row>
     <row r="1122">
@@ -22838,7 +22838,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1122" t="str">
-        <v>כלי ציור על מפה: פוליגון פתוח - דקירת נקודות שמתחברות בקו, בלי סגירה לראשונה</v>
+        <v>כלי ציור על מפה: פוליגון סגור - דקירת נקודות שמתחברות בקו, והאחרונה נסגרת לראשונה</v>
       </c>
       <c r="E1122" t="str">
         <v>כן</v>
@@ -22852,19 +22852,19 @@
         <v/>
       </c>
       <c r="B1123" t="str">
-        <v>2026-09-19 16:54</v>
+        <v>2026-09-19 16:44</v>
       </c>
       <c r="C1123" t="str">
         <v>תכולה חדשה</v>
       </c>
       <c r="D1123" t="str">
-        <v>פ"מ שכבר בנקודת העברה ונגרר לנקודת העברה מעמדה אחרת - טופס תיאום בעמדה הגוררת (מאושר/לא אושר); באישור ההקצאה הקודמת נמחקת</v>
+        <v>כלי ציור על מפה: פוליגון פתוח - דקירת נקודות שמתחברות בקו, בלי סגירה לראשונה</v>
       </c>
       <c r="E1123" t="str">
         <v>כן</v>
       </c>
       <c r="F1123" t="str">
-        <v>server/routes/transferTakeovers.js + TransferTakeoverDialog</v>
+        <v>REFACTOR_LOG #052</v>
       </c>
     </row>
     <row r="1124">
@@ -22878,7 +22878,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1124" t="str">
-        <v>באותו מקרה - התראה עם אישור/דחייה גם בעמדה שהפ"מ כבר אצלה בדרך לנקודת העברה</v>
+        <v>פ"מ שכבר בנקודת העברה ונגרר לנקודת העברה מעמדה אחרת - טופס תיאום בעמדה הגוררת (מאושר/לא אושר); באישור ההקצאה הקודמת נמחקת</v>
       </c>
       <c r="E1124" t="str">
         <v>כן</v>
@@ -22898,7 +22898,7 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1125" t="str">
-        <v>גרירת פ"מ לעמדה/מפה (לא דרך העברה) כשהוא קיים גם בעמדה אחרת - הודעה "שים לב פ"מ X נמצא גם בעמדה Y"</v>
+        <v>באותו מקרה - התראה עם אישור/דחייה גם בעמדה שהפ"מ כבר אצלה בדרך לנקודת העברה</v>
       </c>
       <c r="E1125" t="str">
         <v>כן</v>
@@ -22907,9 +22907,29 @@
         <v>server/routes/transferTakeovers.js + TransferTakeoverDialog</v>
       </c>
     </row>
+    <row r="1126">
+      <c r="A1126" t="str">
+        <v/>
+      </c>
+      <c r="B1126" t="str">
+        <v>2026-09-19 16:54</v>
+      </c>
+      <c r="C1126" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1126" t="str">
+        <v>גרירת פ"מ לעמדה/מפה (לא דרך העברה) כשהוא קיים גם בעמדה אחרת - הודעה "שים לב פ"מ X נמצא גם בעמדה Y"</v>
+      </c>
+      <c r="E1126" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1126" t="str">
+        <v>server/routes/transferTakeovers.js + TransferTakeoverDialog</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1125"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1126"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1124"/>
+  <dimension ref="A1:F1125"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22887,9 +22887,29 @@
         <v>server/routes/transferTakeovers.js + TransferTakeoverDialog</v>
       </c>
     </row>
+    <row r="1125">
+      <c r="A1125" t="str">
+        <v/>
+      </c>
+      <c r="B1125" t="str">
+        <v>2026-09-20 11:54</v>
+      </c>
+      <c r="C1125" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1125" t="str">
+        <v>להשמיע למשתמש את ההתרעות הקוליות של אפליקציית הנהג בהתקרבות לרמזור</v>
+      </c>
+      <c r="E1125" t="str">
+        <v/>
+      </c>
+      <c r="F1125" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1124"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1125"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1125"/>
+  <dimension ref="A1:F1126"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22892,24 +22892,44 @@
         <v/>
       </c>
       <c r="B1125" t="str">
+        <v>2026-09-20 11:53</v>
+      </c>
+      <c r="C1125" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1125" t="str">
+        <v>תצוגת טבלה: לטבלאות בן (מטוסים, נקודות מכוון) גלילה צידית עצמאית, שאינה משפיעה על הגלילה הצידית של טבלת הפ"מים ולהפך</v>
+      </c>
+      <c r="E1125" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1125" t="str">
+        <v>גלילה עצמאית - בלוק דביק ברוחב חלון התצוגה</v>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="str">
+        <v/>
+      </c>
+      <c r="B1126" t="str">
         <v>2026-09-20 11:54</v>
       </c>
-      <c r="C1125" t="str">
-        <v>שיפור לתכולה קיימת</v>
-      </c>
-      <c r="D1125" t="str">
+      <c r="C1126" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1126" t="str">
         <v>להשמיע למשתמש את ההתרעות הקוליות של אפליקציית הנהג בהתקרבות לרמזור</v>
       </c>
-      <c r="E1125" t="str">
-        <v/>
-      </c>
-      <c r="F1125" t="str">
+      <c r="E1126" t="str">
+        <v/>
+      </c>
+      <c r="F1126" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1125"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1126"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1126"/>
+  <dimension ref="A1:F1127"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22892,19 +22892,19 @@
         <v/>
       </c>
       <c r="B1125" t="str">
-        <v>2026-09-20 11:53</v>
+        <v>2026-09-20 11:49</v>
       </c>
       <c r="C1125" t="str">
         <v>שיפור לתכולה קיימת</v>
       </c>
       <c r="D1125" t="str">
-        <v>תצוגת טבלה: לטבלאות בן (מטוסים, נקודות מכוון) גלילה צידית עצמאית, שאינה משפיעה על הגלילה הצידית של טבלת הפ"מים ולהפך</v>
+        <v>כלי ציור על מפה: בחירת סגנון קו - רציף / קווים / נקודות / קו-נקודה / איקסים</v>
       </c>
       <c r="E1125" t="str">
         <v>כן</v>
       </c>
       <c r="F1125" t="str">
-        <v>גלילה עצמאית - בלוק דביק ברוחב חלון התצוגה</v>
+        <v>REFACTOR_LOG #053</v>
       </c>
     </row>
     <row r="1126">
@@ -22912,24 +22912,44 @@
         <v/>
       </c>
       <c r="B1126" t="str">
+        <v>2026-09-20 11:53</v>
+      </c>
+      <c r="C1126" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1126" t="str">
+        <v>תצוגת טבלה: לטבלאות בן (מטוסים, נקודות מכוון) גלילה צידית עצמאית, שאינה משפיעה על הגלילה הצידית של טבלת הפ"מים ולהפך</v>
+      </c>
+      <c r="E1126" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1126" t="str">
+        <v>גלילה עצמאית - בלוק דביק ברוחב חלון התצוגה</v>
+      </c>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="str">
+        <v/>
+      </c>
+      <c r="B1127" t="str">
         <v>2026-09-20 11:54</v>
       </c>
-      <c r="C1126" t="str">
-        <v>שיפור לתכולה קיימת</v>
-      </c>
-      <c r="D1126" t="str">
+      <c r="C1127" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1127" t="str">
         <v>להשמיע למשתמש את ההתרעות הקוליות של אפליקציית הנהג בהתקרבות לרמזור</v>
       </c>
-      <c r="E1126" t="str">
-        <v/>
-      </c>
-      <c r="F1126" t="str">
+      <c r="E1127" t="str">
+        <v/>
+      </c>
+      <c r="F1127" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1126"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1127"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -22941,10 +22941,10 @@
         <v>להשמיע למשתמש את ההתרעות הקוליות של אפליקציית הנהג בהתקרבות לרמזור</v>
       </c>
       <c r="E1127" t="str">
-        <v/>
+        <v>כן</v>
       </c>
       <c r="F1127" t="str">
-        <v/>
+        <v>עמוד השמעה מקומי - אותו playHazardSound מ-driver.html</v>
       </c>
     </row>
   </sheetData>

--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1127"/>
+  <dimension ref="A1:F1128"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22947,9 +22947,29 @@
         <v>עמוד השמעה מקומי - אותו playHazardSound מ-driver.html</v>
       </c>
     </row>
+    <row r="1128">
+      <c r="A1128" t="str">
+        <v/>
+      </c>
+      <c r="B1128" t="str">
+        <v>2026-09-20 12:00</v>
+      </c>
+      <c r="C1128" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1128" t="str">
+        <v>ניהול שדה - אלמנט (רמזור): להגדיר לאיזו הצטלבות/נתיב נסיעה/מסלול הוא רלוונטי, למשל "רלוונטי לנתיב X לפני הצומת עם נתיב Y" (לא חובה - רמזור יכול לעמוד באמצע נתיב)</v>
+      </c>
+      <c r="E1128" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1128" t="str">
+        <v>ca7e39c - road_relevance + טופס האלמנט בניהול</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1127"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1128"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1128"/>
+  <dimension ref="A1:F1129"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22967,9 +22967,29 @@
         <v>ca7e39c - road_relevance + טופס האלמנט בניהול</v>
       </c>
     </row>
+    <row r="1129">
+      <c r="A1129" t="str">
+        <v/>
+      </c>
+      <c r="B1129" t="str">
+        <v>2026-09-20 13:56</v>
+      </c>
+      <c r="C1129" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1129" t="str">
+        <v>תצוגת טבלה: טבלת הבן תתחיל בצד ימין מתחת לעמודה השנייה של הפ"מ</v>
+      </c>
+      <c r="E1129" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1129" t="str">
+        <v>הזחה לפי מקום העמודה + עוגן דביק באותו קו</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1128"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1129"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1129"/>
+  <dimension ref="A1:F1130"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -22987,9 +22987,29 @@
         <v>הזחה לפי מקום העמודה + עוגן דביק באותו קו</v>
       </c>
     </row>
+    <row r="1130">
+      <c r="A1130" t="str">
+        <v/>
+      </c>
+      <c r="B1130" t="str">
+        <v>2026-09-20 14:10</v>
+      </c>
+      <c r="C1130" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1130" t="str">
+        <v>תצוגת טבלה: + ו- לפריסת טבלאות בן (ב"מ סגור), ולידם מספר השורות שבטבלה</v>
+      </c>
+      <c r="E1130" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1130" t="str">
+        <v>מונה על הכפתור הראשי + סגירה מהטבלה הפרוסה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1129"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1130"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1130"/>
+  <dimension ref="A1:F1133"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23007,9 +23007,69 @@
         <v>מונה על הכפתור הראשי + סגירה מהטבלה הפרוסה</v>
       </c>
     </row>
+    <row r="1131">
+      <c r="A1131" t="str">
+        <v/>
+      </c>
+      <c r="B1131" t="str">
+        <v>2026-09-20 14:33</v>
+      </c>
+      <c r="C1131" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1131" t="str">
+        <v>מוד טבלה: שדות בני-עריכה מסומנים בקו תחתון ולחיצה פותחת עריכה במקום</v>
+      </c>
+      <c r="E1131" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1131" t="str">
+        <v>קומיט feat(table) - מוד טבלה</v>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="str">
+        <v/>
+      </c>
+      <c r="B1132" t="str">
+        <v>2026-09-20 14:33</v>
+      </c>
+      <c r="C1132" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1132" t="str">
+        <v>מוד טבלה: ENTER מסיים עריכה ושומר את הטקסט</v>
+      </c>
+      <c r="E1132" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1132" t="str">
+        <v>קומיט feat(table) - מוד טבלה</v>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="str">
+        <v/>
+      </c>
+      <c r="B1133" t="str">
+        <v>2026-09-20 14:33</v>
+      </c>
+      <c r="C1133" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1133" t="str">
+        <v>מוד טבלה: ALT+ENTER יורד שורה בשדות רב-שורתיים</v>
+      </c>
+      <c r="E1133" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1133" t="str">
+        <v>קומיט feat(table) - מוד טבלה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1130"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1133"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1133"/>
+  <dimension ref="A1:F1134"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23067,9 +23067,29 @@
         <v>קומיט feat(table) - מוד טבלה</v>
       </c>
     </row>
+    <row r="1134">
+      <c r="A1134" t="str">
+        <v/>
+      </c>
+      <c r="B1134" t="str">
+        <v>2026-09-20 14:37</v>
+      </c>
+      <c r="C1134" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1134" t="str">
+        <v>תצוגת טבלה: לכל טבלת בן + / - שפותח וסוגר רק את השורות; שם הטבלה מוצג תמיד, כמות השורות מוצגת, וב"מ בפתיחה מהפ"מ היא מכווצת</v>
+      </c>
+      <c r="E1134" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1134" t="str">
+        <v>שתי רמות פריסה - expandedSubTableRows</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1133"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1134"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1134"/>
+  <dimension ref="A1:F1136"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23087,9 +23087,49 @@
         <v>שתי רמות פריסה - expandedSubTableRows</v>
       </c>
     </row>
+    <row r="1135">
+      <c r="A1135" t="str">
+        <v/>
+      </c>
+      <c r="B1135" t="str">
+        <v>2026-09-20 14:56</v>
+      </c>
+      <c r="C1135" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1135" t="str">
+        <v>קליק ימני על פ"מ במוד טבלה פותח את תפריט הפעולות לא במיקום המצביע</v>
+      </c>
+      <c r="E1135" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1135" t="str">
+        <v>קומיט fix(table) - AnchoredPopup לשלושת הפופאפים + כפתור ⋮ בעמודת הידיות</v>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="str">
+        <v/>
+      </c>
+      <c r="B1136" t="str">
+        <v>2026-09-20 14:56</v>
+      </c>
+      <c r="C1136" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1136" t="str">
+        <v>כפתור "פעולות קליק ימני" בפאנל הפעולות השמאלי של הפ"מ - למסך מגע</v>
+      </c>
+      <c r="E1136" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1136" t="str">
+        <v>קומיט fix(table) - AnchoredPopup לשלושת הפופאפים + כפתור ⋮ בעמודת הידיות</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1134"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1136"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1136"/>
+  <dimension ref="A1:F1137"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23127,9 +23127,29 @@
         <v>קומיט fix(table) - AnchoredPopup לשלושת הפופאפים + כפתור ⋮ בעמודת הידיות</v>
       </c>
     </row>
+    <row r="1137">
+      <c r="A1137" t="str">
+        <v/>
+      </c>
+      <c r="B1137" t="str">
+        <v>2026-09-20 18:41</v>
+      </c>
+      <c r="C1137" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1137" t="str">
+        <v>מוד טבלה: עמודות גובה והערה אינן מקבלות קו תחתון ואינן נפתחות לעריכה לפי הכללים שנקבעו</v>
+      </c>
+      <c r="E1137" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1137" t="str">
+        <v>קומיט fix(table) - ברירת מחדל לכתיבה + וריאנט טבלה ל-StripControl</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1136"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1137"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1137"/>
+  <dimension ref="A1:F1138"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23147,9 +23147,29 @@
         <v>קומיט fix(table) - ברירת מחדל לכתיבה + וריאנט טבלה ל-StripControl</v>
       </c>
     </row>
+    <row r="1138">
+      <c r="A1138" t="str">
+        <v/>
+      </c>
+      <c r="B1138" t="str">
+        <v>2026-09-21 16:29</v>
+      </c>
+      <c r="C1138" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1138" t="str">
+        <v>אפליקציית נהג - מפת קדרון: רמזור קסורלה אדום על המפה ולא יצאה התרעת התקרבות לנהג</v>
+      </c>
+      <c r="E1138" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1138" t="str">
+        <v>ברירת המחדל לקטגוריה ברמזורים לא כללה "עצור" - shared/tripTracking.js</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1137"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1138"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1137"/>
+  <dimension ref="A1:F1139"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23147,9 +23147,49 @@
         <v>קומיט fix(table) - ברירת מחדל לכתיבה + וריאנט טבלה ל-StripControl</v>
       </c>
     </row>
+    <row r="1138">
+      <c r="A1138" t="str">
+        <v/>
+      </c>
+      <c r="B1138" t="str">
+        <v>2026-09-21 19:30</v>
+      </c>
+      <c r="C1138" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1138" t="str">
+        <v>מוד טבלה: שדה מהקטלוג ("הערה") לא נשמר בלחיצת ENTER - השרת החזיר 500 על מזהה פ"מ עם קידומת</v>
+      </c>
+      <c r="E1138" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1138" t="str">
+        <v>קומיט fix(strip-controls)</v>
+      </c>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="str">
+        <v/>
+      </c>
+      <c r="B1139" t="str">
+        <v>2026-09-21 19:30</v>
+      </c>
+      <c r="C1139" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1139" t="str">
+        <v>מוד טבלה: ALT+ENTER יורד שורה גם בשדה מהקטלוג (התא הפך ל-textarea)</v>
+      </c>
+      <c r="E1139" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1139" t="str">
+        <v>קומיט fix(strip-controls)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1137"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1139"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1139"/>
+  <dimension ref="A1:F1140"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23187,9 +23187,29 @@
         <v>קומיט fix(strip-controls)</v>
       </c>
     </row>
+    <row r="1140">
+      <c r="A1140" t="str">
+        <v/>
+      </c>
+      <c r="B1140" t="str">
+        <v>2026-09-21 19:30</v>
+      </c>
+      <c r="C1140" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1140" t="str">
+        <v>מחק בציור על המפה: מחיקה על עיגול / מלבן / פוליגון סגור או פתוח מוחקת את כל הצורה</v>
+      </c>
+      <c r="E1140" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1140" t="str">
+        <v>REFACTOR_LOG #054</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1139"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1140"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1140"/>
+  <dimension ref="A1:F1141"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23207,9 +23207,29 @@
         <v>REFACTOR_LOG #054</v>
       </c>
     </row>
+    <row r="1141">
+      <c r="A1141" t="str">
+        <v/>
+      </c>
+      <c r="B1141" t="str">
+        <v>2026-09-21 20:10</v>
+      </c>
+      <c r="C1141" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1141" t="str">
+        <v>מוד טבלה: לחיצה על תא גובה פותחת ישר מקלדת ספרות (במקום תיבת טקסט)</v>
+      </c>
+      <c r="E1141" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1141" t="str">
+        <v>קומיט feat(table) - מקלדת ספרות לגובה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1140"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1141"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1141"/>
+  <dimension ref="A1:F1142"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23227,9 +23227,29 @@
         <v>קומיט feat(table) - מקלדת ספרות לגובה</v>
       </c>
     </row>
+    <row r="1142">
+      <c r="A1142" t="str">
+        <v/>
+      </c>
+      <c r="B1142" t="str">
+        <v>2026-09-21 21:04</v>
+      </c>
+      <c r="C1142" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1142" t="str">
+        <v>מוד טבלה: כל השדות בגובה שורה אחת ומיושרים למעלה; תוכן רב-שורתי עד 3 שורות ואז גלילה בתוך התא</v>
+      </c>
+      <c r="E1142" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1142" t="str">
+        <v>קומיט feat(table) - גובה תא</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1141"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1142"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1142"/>
+  <dimension ref="A1:F1143"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23247,9 +23247,29 @@
         <v>קומיט feat(table) - גובה תא</v>
       </c>
     </row>
+    <row r="1143">
+      <c r="A1143" t="str">
+        <v/>
+      </c>
+      <c r="B1143" t="str">
+        <v>2026-09-21 21:05</v>
+      </c>
+      <c r="C1143" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1143" t="str">
+        <v>מחק בציור על המפה: סמן המחק על המפה יוצג בגודל האמיתי שלו ויגדל עם בורר העובי</v>
+      </c>
+      <c r="E1143" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1143" t="str">
+        <v>REFACTOR_LOG #055</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1142"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1143"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1143"/>
+  <dimension ref="A1:F1144"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23267,9 +23267,29 @@
         <v>REFACTOR_LOG #055</v>
       </c>
     </row>
+    <row r="1144">
+      <c r="A1144" t="str">
+        <v/>
+      </c>
+      <c r="B1144" t="str">
+        <v>2026-09-21 21:25</v>
+      </c>
+      <c r="C1144" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1144" t="str">
+        <v>מוד טבלה: עמודת פעולות הפ"מ (⋮, ידית, פריסת טבלאות, פיצול, מיזוג) בשתי עמודות במקום טור אחד - היא שקובעת את גובה השורה</v>
+      </c>
+      <c r="E1144" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1144" t="str">
+        <v>קומיט feat(table) - שתי עמודות</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1143"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1144"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1144"/>
+  <dimension ref="A1:F1145"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23287,9 +23287,29 @@
         <v>קומיט feat(table) - שתי עמודות</v>
       </c>
     </row>
+    <row r="1145">
+      <c r="A1145" t="str">
+        <v/>
+      </c>
+      <c r="B1145" t="str">
+        <v>2026-09-21 21:56</v>
+      </c>
+      <c r="C1145" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1145" t="str">
+        <v>טופס "בהקפה" - לחיצה על ירוקים או שינוי בטופס צריכים להתעדכן בעמדה מיד (optimistic update), לפני תשובת השרת/DB</v>
+      </c>
+      <c r="E1145" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1145" t="str">
+        <v>c2e1047 · v1.0.291</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1144"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1145"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1145"/>
+  <dimension ref="A1:F1148"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23307,9 +23307,69 @@
         <v>c2e1047 · v1.0.291</v>
       </c>
     </row>
+    <row r="1146">
+      <c r="A1146" t="str">
+        <v/>
+      </c>
+      <c r="B1146" t="str">
+        <v>2026-09-21 22:19</v>
+      </c>
+      <c r="C1146" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1146" t="str">
+        <v>פ"מ פרוס לטבלאות: קו ירוק (קונפליקט פתור) מפריד בין שורת הפ"מ לטבלאות שלו - נראה כאילו הטבלאות אינן חלק מהפ"מ</v>
+      </c>
+      <c r="E1146" t="str">
+        <v/>
+      </c>
+      <c r="F1146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="str">
+        <v/>
+      </c>
+      <c r="B1147" t="str">
+        <v>2026-09-21 22:22</v>
+      </c>
+      <c r="C1147" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1147" t="str">
+        <v>מימוש §6 בארכיטקטורה: יומן פעולות מקומיות במאגר המקומי + מנוע סנכרון חזרה לשרת המרכזי + מסך יישוב סתירות</v>
+      </c>
+      <c r="E1147" t="str">
+        <v/>
+      </c>
+      <c r="F1147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="str">
+        <v/>
+      </c>
+      <c r="B1148" t="str">
+        <v>2026-09-21 22:22</v>
+      </c>
+      <c r="C1148" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1148" t="str">
+        <v>כפתור לדימוי נתק מה-DB בעמדה ספציפית בלבד (עמדות אחרות ממשיכות לעבוד מול השרת המרכזי)</v>
+      </c>
+      <c r="E1148" t="str">
+        <v/>
+      </c>
+      <c r="F1148" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1145"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1148"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -23321,10 +23321,10 @@
         <v>פ"מ פרוס לטבלאות: קו ירוק (קונפליקט פתור) מפריד בין שורת הפ"מ לטבלאות שלו - נראה כאילו הטבלאות אינן חלק מהפ"מ</v>
       </c>
       <c r="E1146" t="str">
-        <v/>
+        <v>כן</v>
       </c>
       <c r="F1146" t="str">
-        <v/>
+        <v>8098369</v>
       </c>
     </row>
     <row r="1147">

--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1148"/>
+  <dimension ref="A1:F1149"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23332,19 +23332,19 @@
         <v/>
       </c>
       <c r="B1147" t="str">
-        <v>2026-09-21 22:22</v>
+        <v>2026-09-21 22:20</v>
       </c>
       <c r="C1147" t="str">
-        <v>תכולה חדשה</v>
+        <v>תקלה</v>
       </c>
       <c r="D1147" t="str">
-        <v>מימוש §6 בארכיטקטורה: יומן פעולות מקומיות במאגר המקומי + מנוע סנכרון חזרה לשרת המרכזי + מסך יישוב סתירות</v>
+        <v>פ"מ שמוחזק בכמה עמדות נעלם מהעמדות האחרות כשעמדה אחת שולחת אותו לנקודת העברה ("בהעברה") - ההחזקה בעמדות האחרות צריכה להישאר</v>
       </c>
       <c r="E1147" t="str">
-        <v/>
+        <v>כן</v>
       </c>
       <c r="F1147" t="str">
-        <v/>
+        <v>src/utils/stripTransferView.ts - הטלה פר-עמדה</v>
       </c>
     </row>
     <row r="1148">
@@ -23358,18 +23358,38 @@
         <v>תכולה חדשה</v>
       </c>
       <c r="D1148" t="str">
+        <v>מימוש §6 בארכיטקטורה: יומן פעולות מקומיות במאגר המקומי + מנוע סנכרון חזרה לשרת המרכזי + מסך יישוב סתירות</v>
+      </c>
+      <c r="E1148" t="str">
+        <v/>
+      </c>
+      <c r="F1148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="str">
+        <v/>
+      </c>
+      <c r="B1149" t="str">
+        <v>2026-09-21 22:22</v>
+      </c>
+      <c r="C1149" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1149" t="str">
         <v>כפתור לדימוי נתק מה-DB בעמדה ספציפית בלבד (עמדות אחרות ממשיכות לעבוד מול השרת המרכזי)</v>
       </c>
-      <c r="E1148" t="str">
-        <v/>
-      </c>
-      <c r="F1148" t="str">
+      <c r="E1149" t="str">
+        <v/>
+      </c>
+      <c r="F1149" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1148"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1149"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1149"/>
+  <dimension ref="A1:F1151"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23387,9 +23387,49 @@
         <v/>
       </c>
     </row>
+    <row r="1150">
+      <c r="A1150" t="str">
+        <v/>
+      </c>
+      <c r="B1150" t="str">
+        <v>2026-09-21 22:44</v>
+      </c>
+      <c r="C1150" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1150" t="str">
+        <v>פ"מ בקונפליקט/חריגה מבלוק במוד טבלה - החלק המקובע והחלק הנגלל לא נראים אותו דבר</v>
+      </c>
+      <c r="E1150" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1150" t="str">
+        <v>box-shadow פנימי על התאים; !important של frozen-col גבר על האנימציה</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="str">
+        <v/>
+      </c>
+      <c r="B1151" t="str">
+        <v>2026-09-21 22:44</v>
+      </c>
+      <c r="C1151" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1151" t="str">
+        <v>סרגל תצוגה: "השתק/הפעל התראות בלוקים" ו"השתק/הפעל התראות קונפליקטים"</v>
+      </c>
+      <c r="E1151" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1151" t="str">
+        <v>מקטע "התראות" בתפריט תצוגה; בלוקים הועבר מהגדרות עמדה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1149"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1151"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1151"/>
+  <dimension ref="A1:F1152"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23427,9 +23427,29 @@
         <v>מקטע "התראות" בתפריט תצוגה; בלוקים הועבר מהגדרות עמדה</v>
       </c>
     </row>
+    <row r="1152">
+      <c r="A1152" t="str">
+        <v/>
+      </c>
+      <c r="B1152" t="str">
+        <v>2026-09-22 07:58</v>
+      </c>
+      <c r="C1152" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1152" t="str">
+        <v>השתקת קונפליקטים תשתיק רק את ההבהוב - הסימון "ק" (אדום/ירוק אם פתור) נשאר</v>
+      </c>
+      <c r="E1152" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1152" t="str">
+        <v>דגל הבהוב נפרד מזיהוי הקונפליקט</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1151"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1152"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1152"/>
+  <dimension ref="A1:F1154"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23447,9 +23447,49 @@
         <v>דגל הבהוב נפרד מזיהוי הקונפליקט</v>
       </c>
     </row>
+    <row r="1153">
+      <c r="A1153" t="str">
+        <v/>
+      </c>
+      <c r="B1153" t="str">
+        <v>2026-09-22 08:12</v>
+      </c>
+      <c r="C1153" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1153" t="str">
+        <v>סנכרון אחרי נתק: סתירה נפתרת אוטומטית לפי מי שעודכן אחרון (LWW) - בלי לעצור את הבקר להכרעה</v>
+      </c>
+      <c r="E1153" t="str">
+        <v/>
+      </c>
+      <c r="F1153" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="str">
+        <v/>
+      </c>
+      <c r="B1154" t="str">
+        <v>2026-09-22 08:12</v>
+      </c>
+      <c r="C1154" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1154" t="str">
+        <v>בעמדה מנותקת חייב להיות אפשר לעשות הכל (גרירה לטבלה/מפה, עדכון) - בלי חסימות</v>
+      </c>
+      <c r="E1154" t="str">
+        <v/>
+      </c>
+      <c r="F1154" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1152"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1154"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1154"/>
+  <dimension ref="A1:F1156"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23487,9 +23487,49 @@
         <v/>
       </c>
     </row>
+    <row r="1155">
+      <c r="A1155" t="str">
+        <v/>
+      </c>
+      <c r="B1155" t="str">
+        <v>2026-09-22 08:45</v>
+      </c>
+      <c r="C1155" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1155" t="str">
+        <v>בנתק מדומה לא מצליח להעביר פ"מ לעמדה אחרת - ההעברה נחסמת</v>
+      </c>
+      <c r="E1155" t="str">
+        <v/>
+      </c>
+      <c r="F1155" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="str">
+        <v/>
+      </c>
+      <c r="B1156" t="str">
+        <v>2026-09-22 08:45</v>
+      </c>
+      <c r="C1156" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1156" t="str">
+        <v>בנתק מדומה עדכון הערה וגובה על פ"מ לא נשמר</v>
+      </c>
+      <c r="E1156" t="str">
+        <v/>
+      </c>
+      <c r="F1156" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1154"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1156"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1156"/>
+  <dimension ref="A1:F1158"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23527,9 +23527,49 @@
         <v/>
       </c>
     </row>
+    <row r="1157">
+      <c r="A1157" t="str">
+        <v/>
+      </c>
+      <c r="B1157" t="str">
+        <v>2026-09-22 09:29</v>
+      </c>
+      <c r="C1157" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1157" t="str">
+        <v>מוד תצוגה טבלאי בעמדת "טבלה": בחירת טבלה (מטוסים / נקודות מכוון) שעולה לרמה ראשונה במקום הפ"מ, כל הטבלאות פרוסות</v>
+      </c>
+      <c r="E1157" t="str">
+        <v/>
+      </c>
+      <c r="F1157" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="str">
+        <v/>
+      </c>
+      <c r="B1158" t="str">
+        <v>2026-09-22 09:29</v>
+      </c>
+      <c r="C1158" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1158" t="str">
+        <v>במוד טבלאי - או"ק וטייסת גדולים בצד הטבלה הפרוסה לזיהוי הפ"מ, ושמירת כל לחצני הפעולה (פיצול/קליק ימני)</v>
+      </c>
+      <c r="E1158" t="str">
+        <v/>
+      </c>
+      <c r="F1158" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1156"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1158"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1158"/>
+  <dimension ref="A1:F1161"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23567,9 +23567,69 @@
         <v/>
       </c>
     </row>
+    <row r="1159">
+      <c r="A1159" t="str">
+        <v/>
+      </c>
+      <c r="B1159" t="str">
+        <v>2026-09-22 09:30</v>
+      </c>
+      <c r="C1159" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1159" t="str">
+        <v>בנתק מוצג "אין מאגר מקומי בעמדה - נתק יאפשר צפייה בלבד" - המאגר המקומי לא נוצר</v>
+      </c>
+      <c r="E1159" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1159" t="str">
+        <v>a7416a8 - server/** ו-PGlite הוחרגו מכל קובצי האריזה; שלושה כשלים שקטים</v>
+      </c>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="str">
+        <v/>
+      </c>
+      <c r="B1160" t="str">
+        <v>2026-09-22 09:30</v>
+      </c>
+      <c r="C1160" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1160" t="str">
+        <v>יצירת מאגר מקומי אוטומטית לכל עמדה בעליית העמדה</v>
+      </c>
+      <c r="E1160" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1160" t="str">
+        <v>a7416a8 - אומת באריזה אמיתית: עולה מתוך app.asar.unpacked תוך 14.5ש</v>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="str">
+        <v/>
+      </c>
+      <c r="B1161" t="str">
+        <v>2026-09-22 09:30</v>
+      </c>
+      <c r="C1161" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1161" t="str">
+        <v>מאגר מקומי גם לעמדה שעולה ב-WEB (דפדפן) - המאגר על מחשב העמדה</v>
+      </c>
+      <c r="E1161" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1161" t="str">
+        <v>036d9ce - סוכן עמדה (AGENT: true) + פורט קבוע 5100</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1158"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1161"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1161"/>
+  <dimension ref="A1:F1162"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23627,9 +23627,29 @@
         <v>036d9ce - סוכן עמדה (AGENT: true) + פורט קבוע 5100</v>
       </c>
     </row>
+    <row r="1162">
+      <c r="A1162" t="str">
+        <v/>
+      </c>
+      <c r="B1162" t="str">
+        <v>2026-09-22 12:03</v>
+      </c>
+      <c r="C1162" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1162" t="str">
+        <v>מוד טבלאי גם מהקליק הימני על פ"מ - רק הטבלאות של אותה עמדה, בלי לבחור פריסט תצוגה אחר</v>
+      </c>
+      <c r="E1162" t="str">
+        <v/>
+      </c>
+      <c r="F1162" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1161"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1162"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1162"/>
+  <dimension ref="A1:F1163"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23647,9 +23647,29 @@
         <v/>
       </c>
     </row>
+    <row r="1163">
+      <c r="A1163" t="str">
+        <v/>
+      </c>
+      <c r="B1163" t="str">
+        <v>2026-09-22 15:51</v>
+      </c>
+      <c r="C1163" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1163" t="str">
+        <v>DB מקומי בגרסת ה-WEB: הדף בדפדפן מגלה את סוכן העמדה ומפנה אליו את כל /api</v>
+      </c>
+      <c r="E1163" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1163" t="str">
+        <v>37aef46 - stationAgent.ts + CORS/PNA בסוכן; npm run verify:web-agent 7/7</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1162"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1163"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1163"/>
+  <dimension ref="A1:F1164"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23667,9 +23667,29 @@
         <v>37aef46 - stationAgent.ts + CORS/PNA בסוכן; npm run verify:web-agent 7/7</v>
       </c>
     </row>
+    <row r="1164">
+      <c r="A1164" t="str">
+        <v/>
+      </c>
+      <c r="B1164" t="str">
+        <v>2026-09-22 18:06</v>
+      </c>
+      <c r="C1164" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1164" t="str">
+        <v>DB מקומי בגרסת WEB לא עבד - שלוש חסימות דפדפן: CSP, Local Network Access, ו-CORS</v>
+      </c>
+      <c r="E1164" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1164" t="str">
+        <v>1351a17 + 8685f31 - connect-src, targetAddressSpace, Permissions-Policy; אומת מול Railway החי</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1163"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1164"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1164"/>
+  <dimension ref="A1:F1167"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23672,24 +23672,84 @@
         <v/>
       </c>
       <c r="B1164" t="str">
+        <v>2026-09-22 18:05</v>
+      </c>
+      <c r="C1164" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1164" t="str">
+        <v>אפליקציית הנהג: ההתרעה הקופצת הוצגה אך לא נשמע צליל כלל - התרעת השמע לא עבדה</v>
+      </c>
+      <c r="E1164" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1164" t="str">
+        <v>3df23bb - AudioContext יחיד + unlockAudio + חיווי חסימה</v>
+      </c>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="str">
+        <v/>
+      </c>
+      <c r="B1165" t="str">
+        <v>2026-09-22 18:05</v>
+      </c>
+      <c r="C1165" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1165" t="str">
+        <v>התרעת שמע גם באפליקציה שמנהלת את ההסעות (המגדל) - לא רק אצל הנהג</v>
+      </c>
+      <c r="E1165" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1165" t="str">
+        <v>3df23bb - TripAlertsLayer + כפתור השתקה</v>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="str">
+        <v/>
+      </c>
+      <c r="B1166" t="str">
+        <v>2026-09-22 18:05</v>
+      </c>
+      <c r="C1166" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1166" t="str">
+        <v>רמזור שהופך לירוק: התרעה "רמזור ירוק - ניתן להמשיך בנסיעה"; חוזר לאדום - שוב התרעת עצור</v>
+      </c>
+      <c r="E1166" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1166" t="str">
+        <v>3df23bb - nearOpenElements + toClear</v>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="str">
+        <v/>
+      </c>
+      <c r="B1167" t="str">
         <v>2026-09-22 18:06</v>
       </c>
-      <c r="C1164" t="str">
-        <v>תקלה</v>
-      </c>
-      <c r="D1164" t="str">
+      <c r="C1167" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1167" t="str">
         <v>DB מקומי בגרסת WEB לא עבד - שלוש חסימות דפדפן: CSP, Local Network Access, ו-CORS</v>
       </c>
-      <c r="E1164" t="str">
-        <v>כן</v>
-      </c>
-      <c r="F1164" t="str">
+      <c r="E1167" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1167" t="str">
         <v>1351a17 + 8685f31 - connect-src, targetAddressSpace, Permissions-Policy; אומת מול Railway החי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1164"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1167"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1167"/>
+  <dimension ref="A1:F1170"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23747,9 +23747,69 @@
         <v>1351a17 + 8685f31 - connect-src, targetAddressSpace, Permissions-Policy; אומת מול Railway החי</v>
       </c>
     </row>
+    <row r="1168">
+      <c r="A1168" t="str">
+        <v/>
+      </c>
+      <c r="B1168" t="str">
+        <v>2026-09-22 18:30</v>
+      </c>
+      <c r="C1168" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1168" t="str">
+        <v>HTTP 502 בפקד "קשר למאגר" - הפרוקסי של הסוכן לשרת המרכזי נכשל</v>
+      </c>
+      <c r="E1168" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1168" t="str">
+        <v>5bcec5d - המראה נמדדה 10.5ש' מול תקרה של 8 -&gt; 502 תמיד; חולקה ל-12 טבלאות לבקשה</v>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="str">
+        <v/>
+      </c>
+      <c r="B1169" t="str">
+        <v>2026-09-22 18:30</v>
+      </c>
+      <c r="C1169" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1169" t="str">
+        <v>במעבר לנתק כל הנתונים נעלמים - המאגר המקומי ריק כי המראה נפלה תמיד</v>
+      </c>
+      <c r="E1169" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1169" t="str">
+        <v>5bcec5d - המראה נמדדה 10.5ש' מול תקרה של 8 -&gt; 502 תמיד; חולקה ל-12 טבלאות לבקשה</v>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="str">
+        <v/>
+      </c>
+      <c r="B1170" t="str">
+        <v>2026-09-22 18:30</v>
+      </c>
+      <c r="C1170" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1170" t="str">
+        <v>ארכיטקטורה: המרכזי מזין ישירות גם את העמדה וגם את המקומי; בנתק העמדה מדברת רק עם המקומי; בחזרה - מה שרלוונטי לעמדה קובע</v>
+      </c>
+      <c r="E1170" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1170" t="str">
+        <v>5bcec5d - המראה נמדדה 10.5ש' מול תקרה של 8 -&gt; 502 תמיד; חולקה ל-12 טבלאות לבקשה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1167"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1170"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1170"/>
+  <dimension ref="A1:F1171"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23807,9 +23807,29 @@
         <v>5bcec5d - המראה נמדדה 10.5ש' מול תקרה של 8 -&gt; 502 תמיד; חולקה ל-12 טבלאות לבקשה</v>
       </c>
     </row>
+    <row r="1171">
+      <c r="A1171" t="str">
+        <v/>
+      </c>
+      <c r="B1171" t="str">
+        <v>2026-09-22 19:30</v>
+      </c>
+      <c r="C1171" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1171" t="str">
+        <v>דף לצפייה בתוכן המאגר המקומי בעמדה - טבלאות, מספרי שורות ותוכן</v>
+      </c>
+      <c r="E1171" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1171" t="str">
+        <v>3e1e2c4 - /local-db.html + /api/__localdb; נבדק בדפדפן מול סוכן חי</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1170"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1171"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1171"/>
+  <dimension ref="A1:F1172"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23827,9 +23827,29 @@
         <v>3e1e2c4 - /local-db.html + /api/__localdb; נבדק בדפדפן מול סוכן חי</v>
       </c>
     </row>
+    <row r="1172">
+      <c r="A1172" t="str">
+        <v/>
+      </c>
+      <c r="B1172" t="str">
+        <v>2026-09-22 20:10</v>
+      </c>
+      <c r="C1172" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1172" t="str">
+        <v>דף המאגר המקומי מציג "לא נמצא מאגר" גם כשהסוכן רץ - חסימת הדפדפן וחוסר אסימון אינן מובחנות</v>
+      </c>
+      <c r="E1172" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1172" t="str">
+        <v>c020c01 - noopener מנע שכפול sessionStorage; שלוש הודעות נפרדות; אומת מול הייצור</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1171"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1172"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1172"/>
+  <dimension ref="A1:F1174"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23847,9 +23847,49 @@
         <v>c020c01 - noopener מנע שכפול sessionStorage; שלוש הודעות נפרדות; אומת מול הייצור</v>
       </c>
     </row>
+    <row r="1173">
+      <c r="A1173" t="str">
+        <v/>
+      </c>
+      <c r="B1173" t="str">
+        <v>2026-09-22 21:50</v>
+      </c>
+      <c r="C1173" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1173" t="str">
+        <v>שירות רקע בעמדה שמסנכרן את המאגר המקומי מהמרכזי כל הזמן - בלי תלות בדפדפן פתוח או במי שמחובר</v>
+      </c>
+      <c r="E1173" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1173" t="str">
+        <v>9eaeca0 - server/sync/daemon.js + STATION_TOKEN קריאה בלבד; אומת בלי דפדפן</v>
+      </c>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="str">
+        <v/>
+      </c>
+      <c r="B1174" t="str">
+        <v>2026-09-22 21:50</v>
+      </c>
+      <c r="C1174" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1174" t="str">
+        <v>פתיחת כתובת הסוכן מחזירה upstream unreachable ECONNREFUSED 127.0.0.1:5000</v>
+      </c>
+      <c r="E1174" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1174" t="str">
+        <v>b8b3600 - Vite -&gt; dist -&gt; 302 למרכז, בלי מבוי סתום</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1172"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1174"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1174"/>
+  <dimension ref="A1:F1175"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23887,9 +23887,29 @@
         <v>b8b3600 - Vite -&gt; dist -&gt; 302 למרכז, בלי מבוי סתום</v>
       </c>
     </row>
+    <row r="1175">
+      <c r="A1175" t="str">
+        <v/>
+      </c>
+      <c r="B1175" t="str">
+        <v>2026-09-30 13:20</v>
+      </c>
+      <c r="C1175" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1175" t="str">
+        <v>ניקוי הקצאות של עמדה לא עובד טוב - ניקוי חלקי משאיר הקצאות מחוברות לעמדה</v>
+      </c>
+      <c r="E1175" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1175" t="str">
+        <v>תוקן - בחירת הקצאות האזור לפי sza.preset_id ולא לפי המפה הפתוחה</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1174"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1175"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1175"/>
+  <dimension ref="A1:F1176"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23907,9 +23907,29 @@
         <v>תוקן - בחירת הקצאות האזור לפי sza.preset_id ולא לפי המפה הפתוחה</v>
       </c>
     </row>
+    <row r="1176">
+      <c r="A1176" t="str">
+        <v/>
+      </c>
+      <c r="B1176" t="str">
+        <v>2026-10-03 07:00</v>
+      </c>
+      <c r="C1176" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1176" t="str">
+        <v>עמדה רגילה שעולה דרך WEB (בלי סוכן ובלי מאגר מקומי) מציגה "אין קשר למרכז" - למה?</v>
+      </c>
+      <c r="E1176" t="str">
+        <v/>
+      </c>
+      <c r="F1176" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1175"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1176"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1176"/>
+  <dimension ref="A1:F1177"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23927,9 +23927,29 @@
         <v/>
       </c>
     </row>
+    <row r="1177">
+      <c r="A1177" t="str">
+        <v/>
+      </c>
+      <c r="B1177" t="str">
+        <v>2026-10-03 13:50</v>
+      </c>
+      <c r="C1177" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1177" t="str">
+        <v>בעמדה שיש בה הקפה - כשיש מטוסים בהקפה, חלון "בהקפה" ייפתח אוטומטית לתצוגה</v>
+      </c>
+      <c r="E1177" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1177" t="str">
+        <v>d8f44ff · v1.0.341</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1176"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1177"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1177"/>
+  <dimension ref="A1:F1178"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23947,9 +23947,29 @@
         <v>d8f44ff · v1.0.341</v>
       </c>
     </row>
+    <row r="1178">
+      <c r="A1178" t="str">
+        <v/>
+      </c>
+      <c r="B1178" t="str">
+        <v>2026-10-03 13:52</v>
+      </c>
+      <c r="C1178" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1178" t="str">
+        <v>בנתק יזום של העמדה לא מופיעה הודעת נתק מהמרכז מתפרצת בצד שמאל למעלה</v>
+      </c>
+      <c r="E1178" t="str">
+        <v/>
+      </c>
+      <c r="F1178" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1177"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1178"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1178"/>
+  <dimension ref="A1:F1179"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="26.83203125" customWidth="1"/>
     <col min="4" max="4" width="72.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -23967,9 +23967,29 @@
         <v/>
       </c>
     </row>
+    <row r="1179">
+      <c r="A1179" t="str">
+        <v/>
+      </c>
+      <c r="B1179" t="str">
+        <v>2026-10-03 14:55</v>
+      </c>
+      <c r="C1179" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1179" t="str">
+        <v>מסך הכניסה מציג חיווי סנכרון ומנסה לסנכרן למאגר המקומי עוד לפני שהמשתמש התחבר</v>
+      </c>
+      <c r="E1179" t="str">
+        <v>לא תקלה</v>
+      </c>
+      <c r="F1179" t="str">
+        <v>נבדק: מסך הכניסה אינו מסנכרן - רק קורא מצב משני נתיבים מקומיים. המראה רצה בסוכן ללא תלות בכניסה, במכוון. החיווי השגוי נבע מתהליך סוכן ישן (00:45) שקדם לתיקון 1ff582e (07:08)</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1178"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1179"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1179"/>
+  <dimension ref="A1:F1180"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -23987,9 +23987,29 @@
         <v>נבדק: מסך הכניסה אינו מסנכרן - רק קורא מצב משני נתיבים מקומיים. המראה רצה בסוכן ללא תלות בכניסה, במכוון. החיווי השגוי נבע מתהליך סוכן ישן (00:45) שקדם לתיקון 1ff582e (07:08)</v>
       </c>
     </row>
+    <row r="1180">
+      <c r="A1180" t="str">
+        <v/>
+      </c>
+      <c r="B1180" t="str">
+        <v>2026-10-03 15:03</v>
+      </c>
+      <c r="C1180" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1180" t="str">
+        <v>המאגר המקומי יסתנכרן ברציפות ולא כל 5 דקות - גם לפני כניסת משתמש</v>
+      </c>
+      <c r="E1180" t="str">
+        <v/>
+      </c>
+      <c r="F1180" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1179"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1180"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1180"/>
+  <dimension ref="A1:F1181"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="26.83203125" customWidth="1"/>
     <col min="4" max="4" width="72.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="60.83203125" customWidth="1"/>
+    <col min="6" max="6" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24007,9 +24007,29 @@
         <v/>
       </c>
     </row>
+    <row r="1181">
+      <c r="A1181" t="str">
+        <v/>
+      </c>
+      <c r="B1181" t="str">
+        <v>2026-10-03 17:24</v>
+      </c>
+      <c r="C1181" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1181" t="str">
+        <v>דסק חופשי - שורות הרשת (כפתור הגריד) מוצגות תמיד</v>
+      </c>
+      <c r="E1181" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1181" t="str">
+        <v>fix/desk-bgbar-always - סרגל הרקע גלוי תמיד, כפתור הפתיחה הוסר</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1180"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1181"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,15 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1181"/>
-  <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="26.83203125" customWidth="1"/>
-    <col min="4" max="4" width="72.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="40.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:F1182"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24027,9 +24019,29 @@
         <v>fix/desk-bgbar-always - סרגל הרקע גלוי תמיד, כפתור הפתיחה הוסר</v>
       </c>
     </row>
+    <row r="1182">
+      <c r="A1182" t="str">
+        <v/>
+      </c>
+      <c r="B1182" t="str">
+        <v>2026-10-03 17:27</v>
+      </c>
+      <c r="C1182" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1182" t="str">
+        <v>דסק חופשי - רקע ב"מ חלק; בחירת שורות/משבצות נשמרת פר-עמדה</v>
+      </c>
+      <c r="E1182" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1182" t="str">
+        <v>fix/desk-bg-per-station - loadDeskBackground/saveDeskBackground פר presetId</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1181"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1182"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1182"/>
+  <dimension ref="A1:F1184"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.83203125" customWidth="1"/>
+    <col min="3" max="3" width="26.83203125" customWidth="1"/>
+    <col min="4" max="4" width="72.83203125" customWidth="1"/>
+    <col min="5" max="5" width="14.83203125" customWidth="1"/>
+    <col min="6" max="6" width="40.83203125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -24039,9 +24047,49 @@
         <v>fix/desk-bg-per-station - loadDeskBackground/saveDeskBackground פר presetId</v>
       </c>
     </row>
+    <row r="1183">
+      <c r="A1183" t="str">
+        <v/>
+      </c>
+      <c r="B1183" t="str">
+        <v>2026-10-06 03:16</v>
+      </c>
+      <c r="C1183" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1183" t="str">
+        <v>הלאמת אזור זמני: תווית האזור המולאם במרכז הפוליגון ובפונט דק ועדין</v>
+      </c>
+      <c r="E1183" t="str">
+        <v/>
+      </c>
+      <c r="F1183" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="str">
+        <v/>
+      </c>
+      <c r="B1184" t="str">
+        <v>2026-10-06 03:16</v>
+      </c>
+      <c r="C1184" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1184" t="str">
+        <v>אזור מוגבל/סגור: תווית ההגבלה במרכז האזור ובפונט דק ועדין</v>
+      </c>
+      <c r="E1184" t="str">
+        <v/>
+      </c>
+      <c r="F1184" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1182"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1184"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1184"/>
+  <dimension ref="A1:F1185"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="26.83203125" customWidth="1"/>
     <col min="4" max="4" width="72.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="40.83203125" customWidth="1"/>
+    <col min="6" max="6" width="60.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24087,9 +24087,29 @@
         <v/>
       </c>
     </row>
+    <row r="1185">
+      <c r="A1185" t="str">
+        <v/>
+      </c>
+      <c r="B1185" t="str">
+        <v>2026-10-08 07:58</v>
+      </c>
+      <c r="C1185" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1185" t="str">
+        <v>בעמדת Electron ללא אינטרנט רשימת משתמשי המיראז' אינה נמצאת - צריך העתק מקומי של המיראז' במאגר שעל המחשב</v>
+      </c>
+      <c r="E1185" t="str">
+        <v/>
+      </c>
+      <c r="F1185" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1184"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1185"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,14 +397,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1185"/>
+  <dimension ref="A1:F1186"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
     <col min="3" max="3" width="26.83203125" customWidth="1"/>
     <col min="4" max="4" width="72.83203125" customWidth="1"/>
     <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="60.83203125" customWidth="1"/>
+    <col min="6" max="6" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -24107,9 +24107,29 @@
         <v/>
       </c>
     </row>
+    <row r="1186">
+      <c r="A1186" t="str">
+        <v/>
+      </c>
+      <c r="B1186" t="str">
+        <v>2026-10-09 18:19</v>
+      </c>
+      <c r="C1186" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1186" t="str">
+        <v>גלילה בתפריטים/פאנלים (במיוחד פ"מ עמדה) - הכותרת וכפתורי הכיווץ נשארים קבועים למעלה ולא נגללים החוצה</v>
+      </c>
+      <c r="E1186" t="str">
+        <v/>
+      </c>
+      <c r="F1186" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1185"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1186"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1186"/>
+  <dimension ref="A1:F1187"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -24127,9 +24127,29 @@
         <v/>
       </c>
     </row>
+    <row r="1187">
+      <c r="A1187" t="str">
+        <v/>
+      </c>
+      <c r="B1187" t="str">
+        <v>2026-10-09 18:35</v>
+      </c>
+      <c r="C1187" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1187" t="str">
+        <v>Ctrl+P מציג "צילום המסך נכשל" - צילום הדפדפן נפל על חלון הצצה לעמדה (iframe) ועל canvas מזוהם</v>
+      </c>
+      <c r="E1187" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1187" t="str">
+        <v>src/utils/domCapture.ts</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1186"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1187"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1187"/>
+  <dimension ref="A1:F1188"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -24147,9 +24147,29 @@
         <v>src/utils/domCapture.ts</v>
       </c>
     </row>
+    <row r="1188">
+      <c r="A1188" t="str">
+        <v/>
+      </c>
+      <c r="B1188" t="str">
+        <v>2026-10-09 18:48</v>
+      </c>
+      <c r="C1188" t="str">
+        <v>תקלה</v>
+      </c>
+      <c r="D1188" t="str">
+        <v>ב-WEB המערכת כל הזמן בנתק</v>
+      </c>
+      <c r="E1188" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1188" t="str">
+        <v>עיכוב בודד נספר ככמה כשלים - netStatus.noteFailure + apiRouter.markDown לפי sentAt</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1187"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1188"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1188"/>
+  <dimension ref="A1:F1190"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -24167,9 +24167,49 @@
         <v>עיכוב בודד נספר ככמה כשלים - netStatus.noteFailure + apiRouter.markDown לפי sentAt</v>
       </c>
     </row>
+    <row r="1189">
+      <c r="A1189" t="str">
+        <v/>
+      </c>
+      <c r="B1189" t="str">
+        <v>2026-10-13 17:11</v>
+      </c>
+      <c r="C1189" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1189" t="str">
+        <v>מפה עם אזורים - כפתור בסרגל לבהירות טקסט שם האזור; ברירת מחדל בהיר חלש (אפור כמו הגבול)</v>
+      </c>
+      <c r="E1189" t="str">
+        <v/>
+      </c>
+      <c r="F1189" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="str">
+        <v/>
+      </c>
+      <c r="B1190" t="str">
+        <v>2026-10-13 17:11</v>
+      </c>
+      <c r="C1190" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1190" t="str">
+        <v>הלאמת אזור זמני ואזור מוגבל - שם האזור מוצג בתוך האזור ובהיר יותר</v>
+      </c>
+      <c r="E1190" t="str">
+        <v/>
+      </c>
+      <c r="F1190" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1188"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1190"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1190"/>
+  <dimension ref="A1:F1192"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -24207,9 +24207,49 @@
         <v/>
       </c>
     </row>
+    <row r="1191">
+      <c r="A1191" t="str">
+        <v/>
+      </c>
+      <c r="B1191" t="str">
+        <v>2026-10-13 23:24</v>
+      </c>
+      <c r="C1191" t="str">
+        <v>שיפור לתכולה קיימת</v>
+      </c>
+      <c r="D1191" t="str">
+        <v>מפה עם אזורים - אפשרות להסתיר לגמרי את טקסט שמות האזורים</v>
+      </c>
+      <c r="E1191" t="str">
+        <v/>
+      </c>
+      <c r="F1191" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="str">
+        <v/>
+      </c>
+      <c r="B1192" t="str">
+        <v>2026-10-13 23:24</v>
+      </c>
+      <c r="C1192" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1192" t="str">
+        <v>מפה עם אזורים - כפתור לשליטה בעובי קווי האזורים</v>
+      </c>
+      <c r="E1192" t="str">
+        <v/>
+      </c>
+      <c r="F1192" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1190"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1192"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/project-requirements.xlsx
+++ b/project-requirements.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1192"/>
+  <dimension ref="A1:F1193"/>
   <cols>
     <col min="1" max="1" width="8.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -24247,9 +24247,29 @@
         <v/>
       </c>
     </row>
+    <row r="1193">
+      <c r="A1193" t="str">
+        <v/>
+      </c>
+      <c r="B1193" t="str">
+        <v>2026-10-13 23:38</v>
+      </c>
+      <c r="C1193" t="str">
+        <v>תכולה חדשה</v>
+      </c>
+      <c r="D1193" t="str">
+        <v>הגדרות כלליות: קטלוג מרוכז של כל כפתורי העמדה + דגל מוצג/מוסתר לכל כפתור, להסתרה גורפת בכל העמדות</v>
+      </c>
+      <c r="E1193" t="str">
+        <v>כן</v>
+      </c>
+      <c r="F1193" t="str">
+        <v>shared/hiddenActions.js + HiddenActionsSection</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F1192"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F1193"/>
   </ignoredErrors>
 </worksheet>
 </file>